--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA924E2-A060-4E8E-AF43-3C1E3E606425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B0028-0E14-4321-A902-2053E74E516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4250" uniqueCount="3911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4334" uniqueCount="3933">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -11994,6 +11994,72 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#PorrasJS2025a</t>
+  </si>
+  <si>
+    <t>Restos Pre-Colombinos y moluscos en la localidad de Corralito, Estado Falcón.</t>
+  </si>
+  <si>
+    <t>Información recopilada por Tulio Peraza 2000</t>
+  </si>
+  <si>
+    <t>Re-exploratory results in the Caipe Field, Barinas – Apure Basin, Venezuela.</t>
+  </si>
+  <si>
+    <t>Chacín, E.; Alvarez, P.</t>
+  </si>
+  <si>
+    <t>Eoceno Superior de Venezuela Suroccidental.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorena de Monrroy y Emira Cabrera </t>
+  </si>
+  <si>
+    <t>Borrador, Corpoven S.A., 1998.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibración de las zonas de nannoplancton calcáreo en la Subcuenca de Agua Salada, Falcón oriental. </t>
+  </si>
+  <si>
+    <t>VII Congreso Geológico Venezolano, Barquisimeto, 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El huerto familiar en armonía con el ambiente. </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 13, Julio – Agosto de 1983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germán Jiménez Ureña: 1861 – 1929. Vida y obra del Ingeniero Germán Jiménez Ureña. </t>
+  </si>
+  <si>
+    <t>La cueva El Samán en Perijá, mide 18,2 kilómetros. Hace tres décadas se exploró la mayor caverna del norte de Venezuela.</t>
+  </si>
+  <si>
+    <t>Rafael Carreňo</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#ChacinEAlvarezP2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MonroyZCabreraE1998</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranI1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d?page_y=0</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#CarrenoR2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/</t>
   </si>
 </sst>
 </file>
@@ -12390,14 +12456,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1068"/>
+  <dimension ref="A1:H1132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
     <col min="3" max="3" width="21.77734375" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="47.5546875" style="4" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="55.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37950,7 +38016,7 @@
         <v>3775</v>
       </c>
       <c r="G1026" s="3" t="str">
-        <f t="shared" ref="G1026:G1068" si="32">HYPERLINK(F1026)</f>
+        <f t="shared" ref="G1026:G1075" si="32">HYPERLINK(F1026)</f>
         <v>https://mariantoc.github.io/stratigraphy.html#Anonimo2001</v>
       </c>
     </row>
@@ -38006,7 +38072,7 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1029">
-        <f t="shared" ref="A1029:A1068" si="33">A1028+1</f>
+        <f t="shared" ref="A1029:A1075" si="33">A1028+1</f>
         <v>1028</v>
       </c>
       <c r="B1029" t="s">
@@ -38962,7 +39028,7 @@
       <c r="E1067" t="s">
         <v>3908</v>
       </c>
-      <c r="F1067" s="5" t="s">
+      <c r="F1067" t="s">
         <v>3909</v>
       </c>
       <c r="G1067" s="3" t="str">
@@ -38987,12 +39053,469 @@
       <c r="E1068" t="s">
         <v>3907</v>
       </c>
-      <c r="F1068" s="5" t="s">
+      <c r="F1068" t="s">
         <v>3910</v>
       </c>
       <c r="G1068" s="3" t="str">
         <f t="shared" si="32"/>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#PorrasJS2025a</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1069">
+        <f t="shared" si="33"/>
+        <v>1068</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>3911</v>
+      </c>
+      <c r="C1069" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D1069">
+        <v>2000</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>3912</v>
+      </c>
+      <c r="F1069" s="5" t="s">
+        <v>3925</v>
+      </c>
+      <c r="G1069" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2000</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1070">
+        <f t="shared" si="33"/>
+        <v>1069</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>3913</v>
+      </c>
+      <c r="C1070" t="s">
+        <v>3914</v>
+      </c>
+      <c r="D1070">
+        <v>2006</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1070" s="5" t="s">
+        <v>3926</v>
+      </c>
+      <c r="G1070" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#ChacinEAlvarezP2006</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1071">
+        <f t="shared" si="33"/>
+        <v>1070</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>3915</v>
+      </c>
+      <c r="C1071" t="s">
+        <v>3916</v>
+      </c>
+      <c r="D1071">
+        <v>1998</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>3917</v>
+      </c>
+      <c r="F1071" s="5" t="s">
+        <v>3927</v>
+      </c>
+      <c r="G1071" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MonroyZCabreraE1998</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1072">
+        <f t="shared" si="33"/>
+        <v>1071</v>
+      </c>
+      <c r="B1072" t="s">
+        <v>3918</v>
+      </c>
+      <c r="C1072" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1072">
+        <v>1989</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>3919</v>
+      </c>
+      <c r="F1072" s="5" t="s">
+        <v>3928</v>
+      </c>
+      <c r="G1072" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranI1989</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1073">
+        <f t="shared" si="33"/>
+        <v>1072</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>3920</v>
+      </c>
+      <c r="D1073">
+        <v>1983</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>3921</v>
+      </c>
+      <c r="F1073" s="5" t="s">
+        <v>3929</v>
+      </c>
+      <c r="G1073" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1983</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1074">
+        <f t="shared" si="33"/>
+        <v>1073</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>3922</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D1074">
+        <v>2025</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>3774</v>
+      </c>
+      <c r="F1074" s="5" t="s">
+        <v>3930</v>
+      </c>
+      <c r="G1074" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d?page_y=0</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1075">
+        <f t="shared" si="33"/>
+        <v>1074</v>
+      </c>
+      <c r="B1075" t="s">
+        <v>3923</v>
+      </c>
+      <c r="C1075" t="s">
+        <v>3924</v>
+      </c>
+      <c r="D1075">
+        <v>2024</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1075" s="5" t="s">
+        <v>3931</v>
+      </c>
+      <c r="G1075" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#CarrenoR2024</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1076" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1077" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1078" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1079" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1080" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1081" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1082" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1083" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1084" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1085" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1086" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1087" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1088" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1089" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1089" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1090" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1090" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1091" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1091" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1092" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1092" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1093" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1093" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1094" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1094" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1095" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1095" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1096" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1096" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1097" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1097" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1098" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1098" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1099" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1099" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1100" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1100" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1101" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1101" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1102" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1102" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1103" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1103" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1104" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1104" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1105" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1105" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1106" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1106" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1107" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1107" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1108" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1108" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1109" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1109" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1110" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1110" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1111" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1111" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1112" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1112" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1113" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1113" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1114" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1114" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1115" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1115" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1116" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1116" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1117" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1117" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1118" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1118" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1119" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1119" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1120" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1120" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1121" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1121" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1122" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1122" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1123" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1123" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1124" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1124" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1125" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1125" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1126" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1126" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1127" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1127" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1128" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1128" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1129" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1129" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1130" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1130" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1131" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1131" s="3" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="1132" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1132" s="3" t="s">
+        <v>3932</v>
       </c>
     </row>
   </sheetData>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B0028-0E14-4321-A902-2053E74E516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0B4B7F-D5C2-4152-AB58-648689E43F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -12053,13 +12053,13 @@
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1983</t>
   </si>
   <si>
-    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d?page_y=0</t>
-  </si>
-  <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#CarrenoR2024</t>
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d</t>
   </si>
 </sst>
 </file>
@@ -39078,7 +39078,7 @@
       <c r="E1069" t="s">
         <v>3912</v>
       </c>
-      <c r="F1069" s="5" t="s">
+      <c r="F1069" t="s">
         <v>3925</v>
       </c>
       <c r="G1069" s="3" t="str">
@@ -39103,7 +39103,7 @@
       <c r="E1070" t="s">
         <v>151</v>
       </c>
-      <c r="F1070" s="5" t="s">
+      <c r="F1070" t="s">
         <v>3926</v>
       </c>
       <c r="G1070" s="3" t="str">
@@ -39128,7 +39128,7 @@
       <c r="E1071" t="s">
         <v>3917</v>
       </c>
-      <c r="F1071" s="5" t="s">
+      <c r="F1071" t="s">
         <v>3927</v>
       </c>
       <c r="G1071" s="3" t="str">
@@ -39153,7 +39153,7 @@
       <c r="E1072" t="s">
         <v>3919</v>
       </c>
-      <c r="F1072" s="5" t="s">
+      <c r="F1072" t="s">
         <v>3928</v>
       </c>
       <c r="G1072" s="3" t="str">
@@ -39175,7 +39175,7 @@
       <c r="E1073" t="s">
         <v>3921</v>
       </c>
-      <c r="F1073" s="5" t="s">
+      <c r="F1073" t="s">
         <v>3929</v>
       </c>
       <c r="G1073" s="3" t="str">
@@ -39201,11 +39201,11 @@
         <v>3774</v>
       </c>
       <c r="F1074" s="5" t="s">
-        <v>3930</v>
+        <v>3932</v>
       </c>
       <c r="G1074" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d?page_y=0</v>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
@@ -39225,8 +39225,8 @@
       <c r="E1075" t="s">
         <v>372</v>
       </c>
-      <c r="F1075" s="5" t="s">
-        <v>3931</v>
+      <c r="F1075" t="s">
+        <v>3930</v>
       </c>
       <c r="G1075" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39235,287 +39235,287 @@
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1076" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1077" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1078" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1079" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1080" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1081" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1082" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1083" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1084" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1085" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1086" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1087" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1088" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1089" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1089" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1090" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1090" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1091" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1091" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1092" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1092" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1093" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1093" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1094" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1094" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1095" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1095" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1096" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1096" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1097" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1097" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1098" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1098" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1099" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1099" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1100" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1100" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1101" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1101" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1102" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1102" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1103" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1103" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1104" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1104" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1105" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1105" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1106" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1106" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1107" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1107" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1108" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1108" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1109" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1109" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1110" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1110" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1111" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1111" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1112" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1112" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1113" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1113" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1114" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1114" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1115" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1115" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1116" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1116" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1117" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1117" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1118" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1118" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1119" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1119" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1120" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1120" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1121" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1121" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1122" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1122" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1123" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1123" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1124" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1124" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1125" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1125" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1126" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1126" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1127" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1127" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1128" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1128" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1129" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1129" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1130" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1130" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1131" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1131" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="1132" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F1132" s="3" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
     </row>
   </sheetData>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0B4B7F-D5C2-4152-AB58-648689E43F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3115E4B-6B70-42E3-9401-B713F0C14A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4334" uniqueCount="3933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4355" uniqueCount="3959">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12060,6 +12060,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d</t>
+  </si>
+  <si>
+    <t>Los arrecifes coralinos: un mundo microbiológico por descubrir. Situación de los corales en el Mar Caribe y Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernández, M.; Bendayan, A.; Lugo, R. </t>
+  </si>
+  <si>
+    <t>Bitácora. Revista del Instituto de Investigaciones Científicas (IVIC). Edición Especial Número 30, Febrero 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El poblamiento temprano de América: Venezuela controversia continental. </t>
+  </si>
+  <si>
+    <t>Arturo Jaimes</t>
+  </si>
+  <si>
+    <t>Predicción de calidad de roca reservorio en areniscas cuarzosas mediante el modelaje diagenético: Aplicación en el área exploratoria de Urica – Mundo Nuevo, Cuenca Oriental de Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">González, S.; Olivares, C.; Sánchez, J. H. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibration of Paleogene palynological zones to the marine time scale. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crux, J. A.; Colmenares, O. </t>
+  </si>
+  <si>
+    <t>Borrador, Ciencias de La Tierra, Intevep, 1995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencia tecnológica. Caso PDVSA. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luisa Mendoza </t>
+  </si>
+  <si>
+    <t>Petromine Internacional. Número 1, Año 1, Septiembre 1990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indice de prospectos y yacimientos de Lagoven S.A. </t>
+  </si>
+  <si>
+    <t>Francisco Moreno</t>
+  </si>
+  <si>
+    <t>Presentación Lagoven S.A., Departamento de Producción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis secuencial de una sección del Mioceno – Plioceno, cerca de Cumarebo, basado en el estudio de foraminíferos y nannoplancton calcáreo. </t>
+  </si>
+  <si>
+    <t>Giffuni, G.; Díaz de Gamero, L.; Castro Mora, M.</t>
+  </si>
+  <si>
+    <t>Trabajo de colaboración Lagoven S.A. y la ilustre Universidad Central de Venezuela, 1992.</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#FernandezMetal2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#JaimesA2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GonzalezSetal2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CruxJColmenareso1995</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#MendozaL1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/fields.html#MorenoF1975</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GiffuniGetal1992</t>
   </si>
 </sst>
 </file>
@@ -38016,7 +38094,7 @@
         <v>3775</v>
       </c>
       <c r="G1026" s="3" t="str">
-        <f t="shared" ref="G1026:G1075" si="32">HYPERLINK(F1026)</f>
+        <f t="shared" ref="G1026:G1082" si="32">HYPERLINK(F1026)</f>
         <v>https://mariantoc.github.io/stratigraphy.html#Anonimo2001</v>
       </c>
     </row>
@@ -38072,7 +38150,7 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1029">
-        <f t="shared" ref="A1029:A1075" si="33">A1028+1</f>
+        <f t="shared" ref="A1029:A1082" si="33">A1028+1</f>
         <v>1028</v>
       </c>
       <c r="B1029" t="s">
@@ -39200,7 +39278,7 @@
       <c r="E1074" t="s">
         <v>3774</v>
       </c>
-      <c r="F1074" s="5" t="s">
+      <c r="F1074" t="s">
         <v>3932</v>
       </c>
       <c r="G1074" s="3" t="str">
@@ -39234,38 +39312,178 @@
       </c>
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1076" s="3" t="s">
-        <v>3931</v>
+      <c r="A1076">
+        <f t="shared" si="33"/>
+        <v>1075</v>
+      </c>
+      <c r="B1076" t="s">
+        <v>3933</v>
+      </c>
+      <c r="C1076" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D1076">
+        <v>2024</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>3935</v>
+      </c>
+      <c r="F1076" s="5" t="s">
+        <v>3952</v>
+      </c>
+      <c r="G1076" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#FernandezMetal2024</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1077" s="3" t="s">
-        <v>3931</v>
+      <c r="A1077">
+        <f t="shared" si="33"/>
+        <v>1076</v>
+      </c>
+      <c r="B1077" t="s">
+        <v>3936</v>
+      </c>
+      <c r="C1077" t="s">
+        <v>3937</v>
+      </c>
+      <c r="D1077">
+        <v>2024</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>3935</v>
+      </c>
+      <c r="F1077" s="5" t="s">
+        <v>3953</v>
+      </c>
+      <c r="G1077" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#JaimesA2024</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1078" s="3" t="s">
-        <v>3931</v>
+      <c r="A1078">
+        <f t="shared" si="33"/>
+        <v>1077</v>
+      </c>
+      <c r="B1078" t="s">
+        <v>3938</v>
+      </c>
+      <c r="C1078" t="s">
+        <v>3939</v>
+      </c>
+      <c r="D1078">
+        <v>2006</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1078" s="5" t="s">
+        <v>3954</v>
+      </c>
+      <c r="G1078" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GonzalezSetal2006</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1079" s="3" t="s">
-        <v>3931</v>
+      <c r="A1079">
+        <f t="shared" si="33"/>
+        <v>1078</v>
+      </c>
+      <c r="B1079" t="s">
+        <v>3940</v>
+      </c>
+      <c r="C1079" t="s">
+        <v>3941</v>
+      </c>
+      <c r="D1079">
+        <v>1995</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>3942</v>
+      </c>
+      <c r="F1079" s="5" t="s">
+        <v>3955</v>
+      </c>
+      <c r="G1079" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CruxJColmenareso1995</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1080" s="3" t="s">
-        <v>3931</v>
+      <c r="A1080">
+        <f t="shared" si="33"/>
+        <v>1079</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3943</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D1080">
+        <v>1990</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>3945</v>
+      </c>
+      <c r="F1080" s="5" t="s">
+        <v>3956</v>
+      </c>
+      <c r="G1080" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#MendozaL1990</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1081" s="3" t="s">
-        <v>3931</v>
+      <c r="A1081">
+        <f t="shared" si="33"/>
+        <v>1080</v>
+      </c>
+      <c r="B1081" t="s">
+        <v>3946</v>
+      </c>
+      <c r="C1081" t="s">
+        <v>3947</v>
+      </c>
+      <c r="D1081">
+        <v>1975</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>3948</v>
+      </c>
+      <c r="F1081" s="5" t="s">
+        <v>3957</v>
+      </c>
+      <c r="G1081" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/fields.html#MorenoF1975</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1082" s="3" t="s">
-        <v>3931</v>
+      <c r="A1082">
+        <f t="shared" si="33"/>
+        <v>1081</v>
+      </c>
+      <c r="B1082" t="s">
+        <v>3949</v>
+      </c>
+      <c r="C1082" t="s">
+        <v>3950</v>
+      </c>
+      <c r="D1082">
+        <v>1992</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>3951</v>
+      </c>
+      <c r="F1082" s="5" t="s">
+        <v>3958</v>
+      </c>
+      <c r="G1082" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GiffuniGetal1992</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3115E4B-6B70-42E3-9401-B713F0C14A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3348E7-AE95-4A69-9AE5-5E69AAC3C046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4355" uniqueCount="3959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="3985">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12138,6 +12138,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GiffuniGetal1992</t>
+  </si>
+  <si>
+    <t>Potencial de las algas y la naturaleza en el secuestro de carbono. Algae and nature potential in carbon sequestration</t>
+  </si>
+  <si>
+    <t>PetroRenova Indexed. Revista Científica de la Energía, Volumen 1, Número 1, Abril – Junio, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desvanecimiento de la brecha de género en la Universidad Venezolana. </t>
+  </si>
+  <si>
+    <t>Caputo, C.; Vargas, D.; Requena, J.</t>
+  </si>
+  <si>
+    <t>INVERCIENCIA, Marzo 2016, Volúmen 41, Número 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extraterrestrial Remote Sensing and Planetary Processes. </t>
+  </si>
+  <si>
+    <t>Gary Prost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The potential of nannofossils analysis applied to archaeological studies: the case of the Riace’s Bronzes. </t>
+  </si>
+  <si>
+    <t>Fiorentino, A.</t>
+  </si>
+  <si>
+    <t>Journal of Nannoplankton Research, Vol. 20, No. 2, 1998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parque Nacional Serranía de La Neblina. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramiro Royero e Iñigo Narbaiza </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 64, Enero – Marzo, 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biostratigraphy of a Middle Miocene – Pliocene sequence from the Cumarebo Area, Falcon State, northwestern Venezuela. </t>
+  </si>
+  <si>
+    <t>Giffuni, G.; Díaz de Gamero, L.</t>
+  </si>
+  <si>
+    <t>Trabajo de colaboración de Lagoven S.A. y la ilustre Universidad Central de Venezuela</t>
+  </si>
+  <si>
+    <t>Reconocimiento de litofacies aplicando clasificación guiada de datos sísmicos en un campo de crudos pesados en la Cuenca Oriental de Venezuela.</t>
+  </si>
+  <si>
+    <t>Barreto, J.; Espeso, A.; Mezones, A.</t>
+  </si>
+  <si>
+    <t>: IX Simposio Bolivariano de Exploración Petrolera en las Cuencas Andinas y Subandinas, 2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM202</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CaputoCetal2016</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#ProstG2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#FlorentinoA1998</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RoyeroRNarbaizaI1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GiffuniGDiazL1991</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/geophysics.html#BarretoJetal2006</t>
   </si>
 </sst>
 </file>
@@ -38094,7 +38172,7 @@
         <v>3775</v>
       </c>
       <c r="G1026" s="3" t="str">
-        <f t="shared" ref="G1026:G1082" si="32">HYPERLINK(F1026)</f>
+        <f t="shared" ref="G1026:G1089" si="32">HYPERLINK(F1026)</f>
         <v>https://mariantoc.github.io/stratigraphy.html#Anonimo2001</v>
       </c>
     </row>
@@ -38150,7 +38228,7 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1029">
-        <f t="shared" ref="A1029:A1082" si="33">A1028+1</f>
+        <f t="shared" ref="A1029:A1089" si="33">A1028+1</f>
         <v>1028</v>
       </c>
       <c r="B1029" t="s">
@@ -39328,7 +39406,7 @@
       <c r="E1076" t="s">
         <v>3935</v>
       </c>
-      <c r="F1076" s="5" t="s">
+      <c r="F1076" t="s">
         <v>3952</v>
       </c>
       <c r="G1076" s="3" t="str">
@@ -39353,7 +39431,7 @@
       <c r="E1077" t="s">
         <v>3935</v>
       </c>
-      <c r="F1077" s="5" t="s">
+      <c r="F1077" t="s">
         <v>3953</v>
       </c>
       <c r="G1077" s="3" t="str">
@@ -39378,7 +39456,7 @@
       <c r="E1078" t="s">
         <v>151</v>
       </c>
-      <c r="F1078" s="5" t="s">
+      <c r="F1078" t="s">
         <v>3954</v>
       </c>
       <c r="G1078" s="3" t="str">
@@ -39403,7 +39481,7 @@
       <c r="E1079" t="s">
         <v>3942</v>
       </c>
-      <c r="F1079" s="5" t="s">
+      <c r="F1079" t="s">
         <v>3955</v>
       </c>
       <c r="G1079" s="3" t="str">
@@ -39428,7 +39506,7 @@
       <c r="E1080" t="s">
         <v>3945</v>
       </c>
-      <c r="F1080" s="5" t="s">
+      <c r="F1080" t="s">
         <v>3956</v>
       </c>
       <c r="G1080" s="3" t="str">
@@ -39453,7 +39531,7 @@
       <c r="E1081" t="s">
         <v>3948</v>
       </c>
-      <c r="F1081" s="5" t="s">
+      <c r="F1081" t="s">
         <v>3957</v>
       </c>
       <c r="G1081" s="3" t="str">
@@ -39478,7 +39556,7 @@
       <c r="E1082" t="s">
         <v>3951</v>
       </c>
-      <c r="F1082" s="5" t="s">
+      <c r="F1082" t="s">
         <v>3958</v>
       </c>
       <c r="G1082" s="3" t="str">
@@ -39487,111 +39565,251 @@
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1083" s="3" t="s">
-        <v>3931</v>
+      <c r="A1083">
+        <f t="shared" si="33"/>
+        <v>1082</v>
+      </c>
+      <c r="B1083" t="s">
+        <v>3959</v>
+      </c>
+      <c r="C1083" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1083">
+        <v>2025</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>3960</v>
+      </c>
+      <c r="F1083" s="5" t="s">
+        <v>3978</v>
+      </c>
+      <c r="G1083" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM202</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1084" s="3" t="s">
-        <v>3931</v>
+      <c r="A1084">
+        <f t="shared" si="33"/>
+        <v>1083</v>
+      </c>
+      <c r="B1084" t="s">
+        <v>3961</v>
+      </c>
+      <c r="C1084" t="s">
+        <v>3962</v>
+      </c>
+      <c r="D1084">
+        <v>2016</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>3963</v>
+      </c>
+      <c r="F1084" s="5" t="s">
+        <v>3979</v>
+      </c>
+      <c r="G1084" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CaputoCetal2016</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1085" s="3" t="s">
-        <v>3931</v>
+      <c r="A1085">
+        <f t="shared" si="33"/>
+        <v>1084</v>
+      </c>
+      <c r="B1085" t="s">
+        <v>3964</v>
+      </c>
+      <c r="C1085" t="s">
+        <v>3965</v>
+      </c>
+      <c r="D1085">
+        <v>2025</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>3818</v>
+      </c>
+      <c r="F1085" s="5" t="s">
+        <v>3980</v>
+      </c>
+      <c r="G1085" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#ProstG2025</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1086" s="3" t="s">
-        <v>3931</v>
+      <c r="A1086">
+        <f t="shared" si="33"/>
+        <v>1085</v>
+      </c>
+      <c r="B1086" t="s">
+        <v>3966</v>
+      </c>
+      <c r="C1086" t="s">
+        <v>3967</v>
+      </c>
+      <c r="D1086">
+        <v>1998</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>3968</v>
+      </c>
+      <c r="F1086" s="5" t="s">
+        <v>3981</v>
+      </c>
+      <c r="G1086" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#FlorentinoA1998</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1087" s="3" t="s">
-        <v>3931</v>
+      <c r="A1087">
+        <f t="shared" si="33"/>
+        <v>1086</v>
+      </c>
+      <c r="B1087" t="s">
+        <v>3969</v>
+      </c>
+      <c r="C1087" t="s">
+        <v>3970</v>
+      </c>
+      <c r="D1087">
+        <v>1993</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>3971</v>
+      </c>
+      <c r="F1087" s="5" t="s">
+        <v>3982</v>
+      </c>
+      <c r="G1087" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RoyeroRNarbaizaI1993</v>
       </c>
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1088" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1089" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1089" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1090" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1088">
+        <f t="shared" si="33"/>
+        <v>1087</v>
+      </c>
+      <c r="B1088" t="s">
+        <v>3972</v>
+      </c>
+      <c r="C1088" t="s">
+        <v>3973</v>
+      </c>
+      <c r="D1088">
+        <v>1991</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>3974</v>
+      </c>
+      <c r="F1088" s="5" t="s">
+        <v>3983</v>
+      </c>
+      <c r="G1088" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GiffuniGDiazL1991</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1089">
+        <f t="shared" si="33"/>
+        <v>1088</v>
+      </c>
+      <c r="B1089" t="s">
+        <v>3975</v>
+      </c>
+      <c r="C1089" t="s">
+        <v>3976</v>
+      </c>
+      <c r="D1089">
+        <v>2006</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>3977</v>
+      </c>
+      <c r="F1089" s="5" t="s">
+        <v>3984</v>
+      </c>
+      <c r="G1089" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/geophysics.html#BarretoJetal2006</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1090" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1091" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1091" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1092" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1092" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1093" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1093" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1094" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1094" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1095" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1095" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1096" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1096" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1097" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1097" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1098" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1098" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1099" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1099" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1100" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1100" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1101" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1101" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1102" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1102" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1103" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1103" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1104" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1104" s="3" t="s">
         <v>3931</v>
       </c>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3348E7-AE95-4A69-9AE5-5E69AAC3C046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9A0741-3010-42D5-A509-888989E318A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -12197,9 +12197,6 @@
     <t>: IX Simposio Bolivariano de Exploración Petrolera en las Cuencas Andinas y Subandinas, 2006</t>
   </si>
   <si>
-    <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM202</t>
-  </si>
-  <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CaputoCetal2016</t>
   </si>
   <si>
@@ -12216,6 +12213,9 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/geophysics.html#BarretoJetal2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM2025</t>
   </si>
 </sst>
 </file>
@@ -39582,11 +39582,11 @@
         <v>3960</v>
       </c>
       <c r="F1083" s="5" t="s">
-        <v>3978</v>
+        <v>3984</v>
       </c>
       <c r="G1083" s="3" t="str">
         <f t="shared" si="32"/>
-        <v>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM202</v>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM2025</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
@@ -39606,8 +39606,8 @@
       <c r="E1084" t="s">
         <v>3963</v>
       </c>
-      <c r="F1084" s="5" t="s">
-        <v>3979</v>
+      <c r="F1084" t="s">
+        <v>3978</v>
       </c>
       <c r="G1084" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39631,8 +39631,8 @@
       <c r="E1085" t="s">
         <v>3818</v>
       </c>
-      <c r="F1085" s="5" t="s">
-        <v>3980</v>
+      <c r="F1085" t="s">
+        <v>3979</v>
       </c>
       <c r="G1085" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39656,8 +39656,8 @@
       <c r="E1086" t="s">
         <v>3968</v>
       </c>
-      <c r="F1086" s="5" t="s">
-        <v>3981</v>
+      <c r="F1086" t="s">
+        <v>3980</v>
       </c>
       <c r="G1086" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39681,8 +39681,8 @@
       <c r="E1087" t="s">
         <v>3971</v>
       </c>
-      <c r="F1087" s="5" t="s">
-        <v>3982</v>
+      <c r="F1087" t="s">
+        <v>3981</v>
       </c>
       <c r="G1087" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39706,8 +39706,8 @@
       <c r="E1088" t="s">
         <v>3974</v>
       </c>
-      <c r="F1088" s="5" t="s">
-        <v>3983</v>
+      <c r="F1088" t="s">
+        <v>3982</v>
       </c>
       <c r="G1088" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39731,8 +39731,8 @@
       <c r="E1089" t="s">
         <v>3977</v>
       </c>
-      <c r="F1089" s="5" t="s">
-        <v>3984</v>
+      <c r="F1089" t="s">
+        <v>3983</v>
       </c>
       <c r="G1089" s="3" t="str">
         <f t="shared" si="32"/>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9A0741-3010-42D5-A509-888989E318A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC96F27-3746-46BE-9DA3-7631E1A9A399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="3985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4397" uniqueCount="4010">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12194,9 +12194,6 @@
     <t>Barreto, J.; Espeso, A.; Mezones, A.</t>
   </si>
   <si>
-    <t>: IX Simposio Bolivariano de Exploración Petrolera en las Cuencas Andinas y Subandinas, 2006</t>
-  </si>
-  <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CaputoCetal2016</t>
   </si>
   <si>
@@ -12216,6 +12213,84 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/topics.html#CastroM2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planktic Foraminifera of the Cretaceous and Paleocene – Eocene. Part 1: CRETACEOUS. </t>
+  </si>
+  <si>
+    <t>Hans Bolli</t>
+  </si>
+  <si>
+    <t>Curso dictado por el Dr. Hans Bolli en la ilustre Universidad Central de Venezuela, Departamento de Geología entre el 8 y el 24 de Abril de 1985, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planktic foraminifera of the Cretaceous and Paleocene – Eocene. Part 2: PALEOCENE – EOCENE. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso de la bioestratigrafía de nannofósiles en medio-ambientes deltaicos. </t>
+  </si>
+  <si>
+    <t>W. Warren Cooper</t>
+  </si>
+  <si>
+    <t>Gulf Research &amp; Development Company, Houston Technical Services, 1971</t>
+  </si>
+  <si>
+    <t>Una oportunidad de embellecer a Caracas. Proyecto de paisajismo del Río Valle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María A. Torres Pantín </t>
+  </si>
+  <si>
+    <t>Revista Nosotros, Lagoven S.A., Junio 1991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homenaje del Colegio de Ingenieros de Venezuela al Dr. Brígido Natera. </t>
+  </si>
+  <si>
+    <t>Sociedad Venezolana de Geólogos</t>
+  </si>
+  <si>
+    <t>Publicación Especial de la Sociedad Venezolana de Geólogos, Noviembre 1986</t>
+  </si>
+  <si>
+    <t>Consideraciones sobre la Formación Querecual de Venezuela oriental. (Notes on Querecual Formation, Eastern Venezuela).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoris, F. </t>
+  </si>
+  <si>
+    <t>GEOS, Número 29, Memorias de las Jornadas 50° Aniversario de la Escuela de Geología, Minas y Geofísica 1938 – 1988, Caracas, Venezuela, Septiembre 1989</t>
+  </si>
+  <si>
+    <t>Miguel Emilio Palacios; Nuevos datos sobre la primera Escuela de Minas fundada en Guasipati, Estado Bolívar, Venezuela.</t>
+  </si>
+  <si>
+    <t>Noel Mariňo Pardo y Franco Urbani Patat</t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Caracas, Número 66, pp. 83 – 88, Enero – Marzo, 2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CooperW1971</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#TorresMA1991</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#NateraB1986</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#YorisF1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#MarinoNUrbaniF2025</t>
   </si>
 </sst>
 </file>
@@ -38172,7 +38247,7 @@
         <v>3775</v>
       </c>
       <c r="G1026" s="3" t="str">
-        <f t="shared" ref="G1026:G1089" si="32">HYPERLINK(F1026)</f>
+        <f t="shared" ref="G1026:G1090" si="32">HYPERLINK(F1026)</f>
         <v>https://mariantoc.github.io/stratigraphy.html#Anonimo2001</v>
       </c>
     </row>
@@ -38228,7 +38303,7 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1029">
-        <f t="shared" ref="A1029:A1089" si="33">A1028+1</f>
+        <f t="shared" ref="A1029:A1092" si="33">A1028+1</f>
         <v>1028</v>
       </c>
       <c r="B1029" t="s">
@@ -39581,8 +39656,8 @@
       <c r="E1083" t="s">
         <v>3960</v>
       </c>
-      <c r="F1083" s="5" t="s">
-        <v>3984</v>
+      <c r="F1083" t="s">
+        <v>3983</v>
       </c>
       <c r="G1083" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39607,7 +39682,7 @@
         <v>3963</v>
       </c>
       <c r="F1084" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="G1084" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39632,7 +39707,7 @@
         <v>3818</v>
       </c>
       <c r="F1085" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="G1085" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39657,7 +39732,7 @@
         <v>3968</v>
       </c>
       <c r="F1086" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="G1086" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39682,7 +39757,7 @@
         <v>3971</v>
       </c>
       <c r="F1087" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="G1087" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39707,7 +39782,7 @@
         <v>3974</v>
       </c>
       <c r="F1088" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="G1088" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39729,10 +39804,10 @@
         <v>2006</v>
       </c>
       <c r="E1089" t="s">
-        <v>3977</v>
+        <v>151</v>
       </c>
       <c r="F1089" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="G1089" s="3" t="str">
         <f t="shared" si="32"/>
@@ -39740,38 +39815,178 @@
       </c>
     </row>
     <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1090" s="3" t="s">
-        <v>3931</v>
+      <c r="A1090">
+        <f t="shared" si="33"/>
+        <v>1089</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>3984</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>3985</v>
+      </c>
+      <c r="D1090">
+        <v>1985</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>3986</v>
+      </c>
+      <c r="F1090" s="5" t="s">
+        <v>4003</v>
+      </c>
+      <c r="G1090" s="3" t="str">
+        <f t="shared" si="32"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985a</v>
       </c>
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1091" s="3" t="s">
-        <v>3931</v>
+      <c r="A1091">
+        <f t="shared" si="33"/>
+        <v>1090</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>3987</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>3985</v>
+      </c>
+      <c r="D1091">
+        <v>1985</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>3986</v>
+      </c>
+      <c r="F1091" s="5" t="s">
+        <v>4004</v>
+      </c>
+      <c r="G1091" s="3" t="str">
+        <f t="shared" ref="G1091:G1096" si="34">HYPERLINK(F1091)</f>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1092" s="3" t="s">
-        <v>3931</v>
+      <c r="A1092">
+        <f t="shared" si="33"/>
+        <v>1091</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>3988</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>3989</v>
+      </c>
+      <c r="D1092">
+        <v>1971</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>3990</v>
+      </c>
+      <c r="F1092" s="5" t="s">
+        <v>4005</v>
+      </c>
+      <c r="G1092" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CooperW1971</v>
       </c>
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1093" s="3" t="s">
-        <v>3931</v>
+      <c r="A1093">
+        <f t="shared" ref="A1093:A1096" si="35">A1092+1</f>
+        <v>1092</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>3991</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>3992</v>
+      </c>
+      <c r="D1093">
+        <v>1991</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>3993</v>
+      </c>
+      <c r="F1093" s="5" t="s">
+        <v>4006</v>
+      </c>
+      <c r="G1093" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#TorresMA1991</v>
       </c>
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1094" s="3" t="s">
-        <v>3931</v>
+      <c r="A1094">
+        <f t="shared" si="35"/>
+        <v>1093</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>3994</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>3995</v>
+      </c>
+      <c r="D1094">
+        <v>1986</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>3996</v>
+      </c>
+      <c r="F1094" s="5" t="s">
+        <v>4007</v>
+      </c>
+      <c r="G1094" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#NateraB1986</v>
       </c>
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1095" s="3" t="s">
-        <v>3931</v>
+      <c r="A1095">
+        <f t="shared" si="35"/>
+        <v>1094</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>3997</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>3998</v>
+      </c>
+      <c r="D1095">
+        <v>1989</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>3999</v>
+      </c>
+      <c r="F1095" s="5" t="s">
+        <v>4008</v>
+      </c>
+      <c r="G1095" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#YorisF1989</v>
       </c>
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1096" s="3" t="s">
-        <v>3931</v>
+      <c r="A1096">
+        <f t="shared" si="35"/>
+        <v>1095</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>4000</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>4001</v>
+      </c>
+      <c r="D1096">
+        <v>2025</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>4002</v>
+      </c>
+      <c r="F1096" s="5" t="s">
+        <v>4009</v>
+      </c>
+      <c r="G1096" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#MarinoNUrbaniF2025</v>
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC96F27-3746-46BE-9DA3-7631E1A9A399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8539313-AB1C-4283-A1B1-BC3AB7C5F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4397" uniqueCount="4010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="4038">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12291,6 +12291,90 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#MarinoNUrbaniF2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El consumidero del rio Guaire, Miranda, Venezuela: un caso histórico de obstrucción de una cueva. </t>
+  </si>
+  <si>
+    <t>Revista Geográfica Venezolana, Universidad de Los Andes, Venezuela, Volumen 46, 2005</t>
+  </si>
+  <si>
+    <t>Actividades geológicas del Dr. Carl Wiedenmayer (1897 – 1951) en el estado Falcón.</t>
+  </si>
+  <si>
+    <t>Urbani, F.; Furrer, M.; Rodríguez, J. A.; Soder, P.</t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 60, Abril 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delta del Orinoco. Tierra de bondades. </t>
+  </si>
+  <si>
+    <t>Freddy Lezama</t>
+  </si>
+  <si>
+    <t>Revisión de las zonas palinológicas U y V de Venezuela (Mioceno Superior – Pleistoceno).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Antonieta Lorente </t>
+  </si>
+  <si>
+    <t>Informe de progreso para Maraven S.A., Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Biofacies development related to upwelling systems based on high resolution biostratigraphic studies in SW Venezuela. Part 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durán, I.; Ruíz, M.; Fasola, A.; Lorente, M.A. </t>
+  </si>
+  <si>
+    <t>Abstract INA Conference Bremen 2000, Journal of Nannoplankton Research, Vol. 22, No. 2, 2000</t>
+  </si>
+  <si>
+    <t>Biofacies development related to upwelling systems based on high resolution biostratigraphic studies in SW Venezuela. Part 2.</t>
+  </si>
+  <si>
+    <t>Cour. Forsch. - Inst. Senckenberg, No. 244, pp. 47 – 59, 2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Excursión Geológica del Departamento de Ciencias de la Tierra de INTEVEP. Geofísica, geología y geoquímica. Camatagua, estado Aragua. </t>
+  </si>
+  <si>
+    <t>INTEVEP S.A., 29 de Septiembre de 1990</t>
+  </si>
+  <si>
+    <t>Nannofósiles calcáreos del Paleógeno de América del Sur. Síntesis bibliográfica hasta 1997.</t>
+  </si>
+  <si>
+    <t>Concheyro, A.; Mostajo, E.</t>
+  </si>
+  <si>
+    <t>Recopilación realizada en colaboración por el Instituto Atlántico Argentino, Departamento de Ciencias Geológicas de Buenos Aires y el Museo Argentino de Ciencias Naturales</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#UrbaniF2005</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniFetal1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#LezamaF1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#LorenteMA1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranIetal2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranIetal2003</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/excursions.html#Intevep1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#ConcheyroAMostajoE1997</t>
   </si>
 </sst>
 </file>
@@ -39831,7 +39915,7 @@
       <c r="E1090" t="s">
         <v>3986</v>
       </c>
-      <c r="F1090" s="5" t="s">
+      <c r="F1090" t="s">
         <v>4003</v>
       </c>
       <c r="G1090" s="3" t="str">
@@ -39856,11 +39940,11 @@
       <c r="E1091" t="s">
         <v>3986</v>
       </c>
-      <c r="F1091" s="5" t="s">
+      <c r="F1091" t="s">
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1096" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1104" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -39881,7 +39965,7 @@
       <c r="E1092" t="s">
         <v>3990</v>
       </c>
-      <c r="F1092" s="5" t="s">
+      <c r="F1092" t="s">
         <v>4005</v>
       </c>
       <c r="G1092" s="3" t="str">
@@ -39891,7 +39975,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1096" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1104" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -39906,7 +39990,7 @@
       <c r="E1093" t="s">
         <v>3993</v>
       </c>
-      <c r="F1093" s="5" t="s">
+      <c r="F1093" t="s">
         <v>4006</v>
       </c>
       <c r="G1093" s="3" t="str">
@@ -39931,7 +40015,7 @@
       <c r="E1094" t="s">
         <v>3996</v>
       </c>
-      <c r="F1094" s="5" t="s">
+      <c r="F1094" t="s">
         <v>4007</v>
       </c>
       <c r="G1094" s="3" t="str">
@@ -39956,7 +40040,7 @@
       <c r="E1095" t="s">
         <v>3999</v>
       </c>
-      <c r="F1095" s="5" t="s">
+      <c r="F1095" t="s">
         <v>4008</v>
       </c>
       <c r="G1095" s="3" t="str">
@@ -39981,7 +40065,7 @@
       <c r="E1096" t="s">
         <v>4002</v>
       </c>
-      <c r="F1096" s="5" t="s">
+      <c r="F1096" t="s">
         <v>4009</v>
       </c>
       <c r="G1096" s="3" t="str">
@@ -39990,43 +40074,200 @@
       </c>
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1097" s="3" t="s">
-        <v>3931</v>
+      <c r="A1097">
+        <f t="shared" si="35"/>
+        <v>1096</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>4010</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1097">
+        <v>2005</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>4011</v>
+      </c>
+      <c r="F1097" s="5" t="s">
+        <v>4030</v>
+      </c>
+      <c r="G1097" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#UrbaniF2005</v>
       </c>
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1098" s="3" t="s">
-        <v>3931</v>
+      <c r="A1098">
+        <f t="shared" si="35"/>
+        <v>1097</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>4012</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>4013</v>
+      </c>
+      <c r="D1098">
+        <v>1997</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>4014</v>
+      </c>
+      <c r="F1098" s="5" t="s">
+        <v>4031</v>
+      </c>
+      <c r="G1098" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniFetal1997</v>
       </c>
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1099" s="3" t="s">
-        <v>3931</v>
+      <c r="A1099">
+        <f t="shared" si="35"/>
+        <v>1098</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>4015</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>4016</v>
+      </c>
+      <c r="D1099">
+        <v>1990</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>3859</v>
+      </c>
+      <c r="F1099" s="5" t="s">
+        <v>4032</v>
+      </c>
+      <c r="G1099" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#LezamaF1990</v>
       </c>
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1100" s="3" t="s">
-        <v>3931</v>
+      <c r="A1100">
+        <f t="shared" si="35"/>
+        <v>1099</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>4017</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>4018</v>
+      </c>
+      <c r="D1100">
+        <v>1982</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>4019</v>
+      </c>
+      <c r="F1100" s="5" t="s">
+        <v>4033</v>
+      </c>
+      <c r="G1100" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#LorenteMA1982</v>
       </c>
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1101" s="3" t="s">
-        <v>3931</v>
+      <c r="A1101">
+        <f t="shared" si="35"/>
+        <v>1100</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>4020</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>4021</v>
+      </c>
+      <c r="D1101">
+        <v>2000</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>4022</v>
+      </c>
+      <c r="F1101" s="5" t="s">
+        <v>4034</v>
+      </c>
+      <c r="G1101" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranIetal2000</v>
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1102" s="3" t="s">
-        <v>3931</v>
+      <c r="A1102">
+        <f t="shared" si="35"/>
+        <v>1101</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>4023</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>4021</v>
+      </c>
+      <c r="D1102">
+        <v>2003</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>4024</v>
+      </c>
+      <c r="F1102" s="5" t="s">
+        <v>4035</v>
+      </c>
+      <c r="G1102" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DuranIetal2003</v>
       </c>
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1103" s="3" t="s">
-        <v>3931</v>
+      <c r="A1103">
+        <f t="shared" si="35"/>
+        <v>1102</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>4025</v>
+      </c>
+      <c r="D1103">
+        <v>1990</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>4026</v>
+      </c>
+      <c r="F1103" s="5" t="s">
+        <v>4036</v>
+      </c>
+      <c r="G1103" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/excursions.html#Intevep1990</v>
       </c>
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1104" s="3" t="s">
-        <v>3931</v>
+      <c r="A1104">
+        <f t="shared" si="35"/>
+        <v>1103</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>4027</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>4028</v>
+      </c>
+      <c r="D1104">
+        <v>1997</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>4029</v>
+      </c>
+      <c r="F1104" s="5" t="s">
+        <v>4037</v>
+      </c>
+      <c r="G1104" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#ConcheyroAMostajoE1997</v>
       </c>
     </row>
     <row r="1105" spans="6:6" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8539313-AB1C-4283-A1B1-BC3AB7C5F391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB69C6-1586-4E0A-A728-62A99A53F861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="4038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4447" uniqueCount="4067">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12375,6 +12375,93 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#ConcheyroAMostajoE1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cueva del Consumidero del Río Guaire. El Encantado, Estado Miranda, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Carroll Wilson (1906 – 1969). La vida de un geólogo pionero y sus exploraciones en Venezuela y Colombia. </t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingeniería y el Hábitat, Caracas, Número 66, pp. 80 – 101, Enero – Marzo 2025</t>
+  </si>
+  <si>
+    <t>Calcareous nannofossils: an invaluable tool in the exploration od the eastern Venezuela Basin.</t>
+  </si>
+  <si>
+    <t>Nieves Di Gianni Canudas</t>
+  </si>
+  <si>
+    <t>Abstract INA Conference Bremen 2000. Journal of Nannoplankton Research Vol.22, No. 2, 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuevo Parque Nacional: Sierra de La Culata. Un ecosistema único en el mundo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aldemaro Romero H. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nociones de economía petrolera. </t>
+  </si>
+  <si>
+    <t>F. Alvarez Chacín</t>
+  </si>
+  <si>
+    <t>Revista de la Universidad del Zulia, Aňo III, Número 9, Mayo – Agosto, 1952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nannoplancton calcáreo de la Formación Punta Gavilán, Estado Falcón, Venezuela. </t>
+  </si>
+  <si>
+    <t>Machado, A.; Marcano, R.; Castro Mora, M.; Padrón, V.</t>
+  </si>
+  <si>
+    <t>Trabajo realizado dentro del plan de estudio de la Escuela de Geología, Minas y Geofísica de la ilustre Universidad Central de Venezuela, 1992</t>
+  </si>
+  <si>
+    <t>Biostratigraphy of 22 wells of Monagas. Eastern Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villain, J. M.; Carney, J.; Castro Mora, M. </t>
+  </si>
+  <si>
+    <t>Preliminary report prepared for publication 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don Francisco de Paula Alamo (1866 – 1943). Un divulgador de la espeleología Venezolana. </t>
+  </si>
+  <si>
+    <t>La baba. Factor de controversia</t>
+  </si>
+  <si>
+    <t>Santiago Ramos</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#UrbaniF1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CasasJE2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DiGianiN2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RomeroA1990</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#AlvarezF1952</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MachadoAetal1992</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#VillainJMetal1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RamosS1990</t>
   </si>
 </sst>
 </file>
@@ -39944,7 +40031,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1104" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1113" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -39975,7 +40062,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1104" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1113" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -40090,7 +40177,7 @@
       <c r="E1097" t="s">
         <v>4011</v>
       </c>
-      <c r="F1097" s="5" t="s">
+      <c r="F1097" t="s">
         <v>4030</v>
       </c>
       <c r="G1097" s="3" t="str">
@@ -40115,7 +40202,7 @@
       <c r="E1098" t="s">
         <v>4014</v>
       </c>
-      <c r="F1098" s="5" t="s">
+      <c r="F1098" t="s">
         <v>4031</v>
       </c>
       <c r="G1098" s="3" t="str">
@@ -40140,7 +40227,7 @@
       <c r="E1099" t="s">
         <v>3859</v>
       </c>
-      <c r="F1099" s="5" t="s">
+      <c r="F1099" t="s">
         <v>4032</v>
       </c>
       <c r="G1099" s="3" t="str">
@@ -40165,7 +40252,7 @@
       <c r="E1100" t="s">
         <v>4019</v>
       </c>
-      <c r="F1100" s="5" t="s">
+      <c r="F1100" t="s">
         <v>4033</v>
       </c>
       <c r="G1100" s="3" t="str">
@@ -40190,7 +40277,7 @@
       <c r="E1101" t="s">
         <v>4022</v>
       </c>
-      <c r="F1101" s="5" t="s">
+      <c r="F1101" t="s">
         <v>4034</v>
       </c>
       <c r="G1101" s="3" t="str">
@@ -40215,7 +40302,7 @@
       <c r="E1102" t="s">
         <v>4024</v>
       </c>
-      <c r="F1102" s="5" t="s">
+      <c r="F1102" t="s">
         <v>4035</v>
       </c>
       <c r="G1102" s="3" t="str">
@@ -40237,7 +40324,7 @@
       <c r="E1103" t="s">
         <v>4026</v>
       </c>
-      <c r="F1103" s="5" t="s">
+      <c r="F1103" t="s">
         <v>4036</v>
       </c>
       <c r="G1103" s="3" t="str">
@@ -40262,7 +40349,7 @@
       <c r="E1104" t="s">
         <v>4029</v>
       </c>
-      <c r="F1104" s="5" t="s">
+      <c r="F1104" t="s">
         <v>4037</v>
       </c>
       <c r="G1104" s="3" t="str">
@@ -40270,82 +40357,262 @@
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#ConcheyroAMostajoE1997</v>
       </c>
     </row>
-    <row r="1105" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1105" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1106" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1106" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1107" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1107" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1108" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1108" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1109" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1109" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1110" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1110" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1111" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1111" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1112" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1112" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1113" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1113" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1114" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1105">
+        <f t="shared" si="35"/>
+        <v>1104</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>4038</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D1105">
+        <v>1997</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>4014</v>
+      </c>
+      <c r="F1105" s="5" t="s">
+        <v>4058</v>
+      </c>
+      <c r="G1105" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#UrbaniF1997</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1106">
+        <f t="shared" si="35"/>
+        <v>1105</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>4039</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>3306</v>
+      </c>
+      <c r="D1106">
+        <v>2025</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>4040</v>
+      </c>
+      <c r="F1106" s="5" t="s">
+        <v>4059</v>
+      </c>
+      <c r="G1106" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CasasJE2025</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1107">
+        <f t="shared" si="35"/>
+        <v>1106</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>4041</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>4042</v>
+      </c>
+      <c r="D1107">
+        <v>2000</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>4043</v>
+      </c>
+      <c r="F1107" s="5" t="s">
+        <v>4060</v>
+      </c>
+      <c r="G1107" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#DiGianiN2000</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1108">
+        <f t="shared" si="35"/>
+        <v>1107</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>4044</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>4045</v>
+      </c>
+      <c r="D1108">
+        <v>1990</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>3859</v>
+      </c>
+      <c r="F1108" s="5" t="s">
+        <v>4061</v>
+      </c>
+      <c r="G1108" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RomeroA1990</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1109">
+        <f t="shared" si="35"/>
+        <v>1108</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>4046</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>4047</v>
+      </c>
+      <c r="D1109">
+        <v>1952</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>4048</v>
+      </c>
+      <c r="F1109" s="5" t="s">
+        <v>4062</v>
+      </c>
+      <c r="G1109" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#AlvarezF1952</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1110">
+        <f t="shared" si="35"/>
+        <v>1109</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>4049</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>4050</v>
+      </c>
+      <c r="D1110">
+        <v>1992</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>4051</v>
+      </c>
+      <c r="F1110" s="5" t="s">
+        <v>4063</v>
+      </c>
+      <c r="G1110" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MachadoAetal1992</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1111">
+        <f t="shared" si="35"/>
+        <v>1110</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>4052</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>4053</v>
+      </c>
+      <c r="D1111">
+        <v>1993</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>4054</v>
+      </c>
+      <c r="F1111" s="5" t="s">
+        <v>4064</v>
+      </c>
+      <c r="G1111" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#VillainJMetal1993</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1112">
+        <f t="shared" si="35"/>
+        <v>1111</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>4055</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D1112">
+        <v>1997</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>4014</v>
+      </c>
+      <c r="F1112" s="5" t="s">
+        <v>4065</v>
+      </c>
+      <c r="G1112" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF1997</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1113">
+        <f t="shared" si="35"/>
+        <v>1112</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>4056</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>4057</v>
+      </c>
+      <c r="D1113">
+        <v>1990</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>3859</v>
+      </c>
+      <c r="F1113" s="5" t="s">
+        <v>4066</v>
+      </c>
+      <c r="G1113" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RamosS1990</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1114" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1115" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1115" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1116" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1116" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1117" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1117" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1118" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1118" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1119" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1119" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1120" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1120" s="3" t="s">
         <v>3931</v>
       </c>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB69C6-1586-4E0A-A728-62A99A53F861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040B8717-0907-4DF7-A60B-E34E190BA0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4447" uniqueCount="4067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="4085">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12462,6 +12462,60 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#RamosS1990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Génesis, litología y mineralogía de depósitos ferríferos con alto grado de metamorfismo. </t>
+  </si>
+  <si>
+    <t>Athenea Journal, Vol. 5, Issue 17, pp. 16 – 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modern pollen deposits in the Venezuelan Andes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Lea Salgado Labouriau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Núñez Avila, E.A.; Bisier Marín, C.A.; López Hércules, J.R.; Stabilito Casares, G.J. </t>
+  </si>
+  <si>
+    <t>Grana 18, pp. 53 – 68, 1979</t>
+  </si>
+  <si>
+    <t>Mapa geológico de la Península de Paria.</t>
+  </si>
+  <si>
+    <t>Modificado por Tulio Peraza, 1999,  para el Código Geológico de Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palinología: esporas y polen fósiles narran el pasado. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Cesari </t>
+  </si>
+  <si>
+    <t>Sample Examination Manual.</t>
+  </si>
+  <si>
+    <t>R. G. Swanson</t>
+  </si>
+  <si>
+    <t>Curso de Lagoven S.A.</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#NunezEAetal2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SalgadoML1979</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/maps.html#SchererW1964</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#CesariC1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SwansonRG1981</t>
   </si>
 </sst>
 </file>
@@ -40031,7 +40085,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1113" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1118" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40062,7 +40116,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1113" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1118" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -40374,7 +40428,7 @@
       <c r="E1105" t="s">
         <v>4014</v>
       </c>
-      <c r="F1105" s="5" t="s">
+      <c r="F1105" t="s">
         <v>4058</v>
       </c>
       <c r="G1105" s="3" t="str">
@@ -40399,7 +40453,7 @@
       <c r="E1106" t="s">
         <v>4040</v>
       </c>
-      <c r="F1106" s="5" t="s">
+      <c r="F1106" t="s">
         <v>4059</v>
       </c>
       <c r="G1106" s="3" t="str">
@@ -40424,7 +40478,7 @@
       <c r="E1107" t="s">
         <v>4043</v>
       </c>
-      <c r="F1107" s="5" t="s">
+      <c r="F1107" t="s">
         <v>4060</v>
       </c>
       <c r="G1107" s="3" t="str">
@@ -40449,7 +40503,7 @@
       <c r="E1108" t="s">
         <v>3859</v>
       </c>
-      <c r="F1108" s="5" t="s">
+      <c r="F1108" t="s">
         <v>4061</v>
       </c>
       <c r="G1108" s="3" t="str">
@@ -40474,7 +40528,7 @@
       <c r="E1109" t="s">
         <v>4048</v>
       </c>
-      <c r="F1109" s="5" t="s">
+      <c r="F1109" t="s">
         <v>4062</v>
       </c>
       <c r="G1109" s="3" t="str">
@@ -40499,7 +40553,7 @@
       <c r="E1110" t="s">
         <v>4051</v>
       </c>
-      <c r="F1110" s="5" t="s">
+      <c r="F1110" t="s">
         <v>4063</v>
       </c>
       <c r="G1110" s="3" t="str">
@@ -40524,7 +40578,7 @@
       <c r="E1111" t="s">
         <v>4054</v>
       </c>
-      <c r="F1111" s="5" t="s">
+      <c r="F1111" t="s">
         <v>4064</v>
       </c>
       <c r="G1111" s="3" t="str">
@@ -40549,7 +40603,7 @@
       <c r="E1112" t="s">
         <v>4014</v>
       </c>
-      <c r="F1112" s="5" t="s">
+      <c r="F1112" t="s">
         <v>4065</v>
       </c>
       <c r="G1112" s="3" t="str">
@@ -40574,7 +40628,7 @@
       <c r="E1113" t="s">
         <v>3859</v>
       </c>
-      <c r="F1113" s="5" t="s">
+      <c r="F1113" t="s">
         <v>4066</v>
       </c>
       <c r="G1113" s="3" t="str">
@@ -40583,28 +40637,128 @@
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1114" s="3" t="s">
-        <v>3931</v>
+      <c r="A1114">
+        <f t="shared" si="35"/>
+        <v>1113</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>4067</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>4071</v>
+      </c>
+      <c r="D1114">
+        <v>2024</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>4068</v>
+      </c>
+      <c r="F1114" s="5" t="s">
+        <v>4080</v>
+      </c>
+      <c r="G1114" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#NunezEAetal2024</v>
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1115" s="3" t="s">
-        <v>3931</v>
+      <c r="A1115">
+        <f t="shared" si="35"/>
+        <v>1114</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>4069</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D1115">
+        <v>1979</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>4072</v>
+      </c>
+      <c r="F1115" s="5" t="s">
+        <v>4081</v>
+      </c>
+      <c r="G1115" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SalgadoML1979</v>
       </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1116" s="3" t="s">
-        <v>3931</v>
+      <c r="A1116">
+        <f t="shared" si="35"/>
+        <v>1115</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>4073</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>746</v>
+      </c>
+      <c r="D1116">
+        <v>1964</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>4074</v>
+      </c>
+      <c r="F1116" s="5" t="s">
+        <v>4082</v>
+      </c>
+      <c r="G1116" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/maps.html#SchererW1964</v>
       </c>
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1117" s="3" t="s">
-        <v>3931</v>
+      <c r="A1117">
+        <f t="shared" si="35"/>
+        <v>1116</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>4075</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>4076</v>
+      </c>
+      <c r="D1117">
+        <v>1993</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>3971</v>
+      </c>
+      <c r="F1117" s="5" t="s">
+        <v>4083</v>
+      </c>
+      <c r="G1117" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#CesariC1993</v>
       </c>
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1118" s="3" t="s">
-        <v>3931</v>
+      <c r="A1118">
+        <f t="shared" si="35"/>
+        <v>1117</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>4077</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>4078</v>
+      </c>
+      <c r="D1118">
+        <v>1981</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>4079</v>
+      </c>
+      <c r="F1118" s="5" t="s">
+        <v>4084</v>
+      </c>
+      <c r="G1118" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SwansonRG1981</v>
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040B8717-0907-4DF7-A60B-E34E190BA0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87668FF1-17DD-45CA-AFC9-C996B64CF7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$778</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4462" uniqueCount="4085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="4107">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12516,6 +12516,72 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SwansonRG1981</t>
+  </si>
+  <si>
+    <t>Tributo a Louis Martin Robert Rutten (1884 – 1946) “De Uitzonderlijke Geoloog”. “El geélogo excepcional”.</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Especial, Julio 2024</t>
+  </si>
+  <si>
+    <t>Rocas Cenozoicas generadoras como producto del adelgazamiento cortical en la Cuenca de Falcón, Venezuela.</t>
+  </si>
+  <si>
+    <t>Baquero, M.; Sousa, J.; Rodríguez, J.; Grobas, J.; Kassabji, E.; Acosta, J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reef Pollution in Paradise. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weiss, M. P.; Goddard, D.A. </t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 17, Números 7, 8 y 9, Julio , Agosto y Septiembre 1974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The age and correlation of the Tertiary sediments of the Paraguana Peninsula, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter, V. F.; Bartok, P. </t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 17, Números 7, 8 y 9, Julio , Agosto y Septiembre 1974.</t>
+  </si>
+  <si>
+    <t>Moluscos en la localidad de Urumaco, estado Falcón, Venezuela.</t>
+  </si>
+  <si>
+    <t>Información recopilada por Tulio Peraza para el Código Estratigráfico Venezolano, 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palinoestratigrafía de los sedimentos Pre-Cretáceos (Formación Carrizal) en el área de Zuata, Venezuela oriental. </t>
+  </si>
+  <si>
+    <t>Revista Técnica de Intevep, 6 (1), pp. 67-89, Enero 1986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geología del Petróleo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guillermo Rodríguez Eraso </t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CasasJE2024</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BaqueroMetal2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#WeissMPGoddardDA1974</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#HunterVFBartokP1974</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SinanogluE1986</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezG1952</t>
   </si>
 </sst>
 </file>
@@ -12588,7 +12654,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -12596,7 +12662,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -12912,7 +12977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1132"/>
+  <dimension ref="A1:H1167"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -40085,7 +40150,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1118" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1125" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40116,7 +40181,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1118" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1127" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -40653,7 +40718,7 @@
       <c r="E1114" t="s">
         <v>4068</v>
       </c>
-      <c r="F1114" s="5" t="s">
+      <c r="F1114" t="s">
         <v>4080</v>
       </c>
       <c r="G1114" s="3" t="str">
@@ -40678,7 +40743,7 @@
       <c r="E1115" t="s">
         <v>4072</v>
       </c>
-      <c r="F1115" s="5" t="s">
+      <c r="F1115" t="s">
         <v>4081</v>
       </c>
       <c r="G1115" s="3" t="str">
@@ -40703,7 +40768,7 @@
       <c r="E1116" t="s">
         <v>4074</v>
       </c>
-      <c r="F1116" s="5" t="s">
+      <c r="F1116" t="s">
         <v>4082</v>
       </c>
       <c r="G1116" s="3" t="str">
@@ -40728,7 +40793,7 @@
       <c r="E1117" t="s">
         <v>3971</v>
       </c>
-      <c r="F1117" s="5" t="s">
+      <c r="F1117" t="s">
         <v>4083</v>
       </c>
       <c r="G1117" s="3" t="str">
@@ -40753,7 +40818,7 @@
       <c r="E1118" t="s">
         <v>4079</v>
       </c>
-      <c r="F1118" s="5" t="s">
+      <c r="F1118" t="s">
         <v>4084</v>
       </c>
       <c r="G1118" s="3" t="str">
@@ -40762,79 +40827,403 @@
       </c>
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1119">
+        <f t="shared" si="35"/>
+        <v>1118</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>4085</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1119">
+        <v>2024</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>4086</v>
+      </c>
       <c r="F1119" s="3" t="s">
-        <v>3931</v>
+        <v>4101</v>
+      </c>
+      <c r="G1119" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CasasJE2024</v>
       </c>
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1120">
+        <f t="shared" si="35"/>
+        <v>1119</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>4087</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>4088</v>
+      </c>
+      <c r="D1120">
+        <v>2006</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>151</v>
+      </c>
       <c r="F1120" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1121" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4102</v>
+      </c>
+      <c r="G1120" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BaqueroMetal2006</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1121">
+        <f t="shared" si="35"/>
+        <v>1120</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>4089</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>4090</v>
+      </c>
+      <c r="D1121">
+        <v>1974</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>4091</v>
+      </c>
       <c r="F1121" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1122" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4103</v>
+      </c>
+      <c r="G1121" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#WeissMPGoddardDA1974</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1122">
+        <f t="shared" si="35"/>
+        <v>1121</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>4092</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>4093</v>
+      </c>
+      <c r="D1122">
+        <v>1974</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>4094</v>
+      </c>
       <c r="F1122" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1123" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4104</v>
+      </c>
+      <c r="G1122" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#HunterVFBartokP1974</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1123">
+        <f t="shared" si="35"/>
+        <v>1122</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>4095</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D1123">
+        <v>2000</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>4096</v>
+      </c>
       <c r="F1123" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1124" spans="6:6" x14ac:dyDescent="0.3">
+        <v>3925</v>
+      </c>
+      <c r="G1123" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2000</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1124">
+        <f t="shared" si="35"/>
+        <v>1123</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>4097</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D1124">
+        <v>1986</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>4098</v>
+      </c>
       <c r="F1124" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1125" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4105</v>
+      </c>
+      <c r="G1124" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SinanogluE1986</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1125">
+        <f t="shared" si="35"/>
+        <v>1124</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>4099</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>4100</v>
+      </c>
+      <c r="D1125">
+        <v>1952</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>4048</v>
+      </c>
       <c r="F1125" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1126" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4106</v>
+      </c>
+      <c r="G1125" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezG1952</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1126" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1127" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1127" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1128" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1128" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1129" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1129" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1130" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1130" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1131" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1131" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1132" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1132" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
+    <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1133" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1134" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1135" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F1136" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1137" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1137" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1138" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1138" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1139" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1139" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1140" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1140" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1141" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1141" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1142" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1142" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1143" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1143" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1144" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1144" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1145" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1145" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1146" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1146" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1147" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1147" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1148" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1148" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1149" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1149" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1150" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1150" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1151" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1151" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1152" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1152" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1153" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1153" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1154" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1154" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1155" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1155" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1156" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1156" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1157" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1157" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1158" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1158" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1159" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1159" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1160" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1160" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1161" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1161" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1162" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1162" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1163" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1163" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1164" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1164" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1165" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1165" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1166" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1166" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="1167" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F1167" s="3" t="s">
+        <v>3931</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G778" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
+  <autoFilter ref="A1:G1167" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F1119" r:id="rId1" location="CasasJE2024" xr:uid="{23A2EEBA-AA10-4E06-9AE1-D6206EC6DEF7}"/>
+    <hyperlink ref="F1120" r:id="rId2" location="BaqueroMetal2006" xr:uid="{C4B730AC-FFF1-47ED-A8CA-CD610C49980C}"/>
+    <hyperlink ref="F1121" r:id="rId3" location="WeissMPGoddardDA1974" xr:uid="{2DDCE41C-126B-4B19-8E0F-015B3CEB1FBB}"/>
+    <hyperlink ref="F1122" r:id="rId4" location="HunterVFBartokP1974" xr:uid="{5EDD6896-49FD-456E-87C5-8650DE3C0D4D}"/>
+    <hyperlink ref="F1123" r:id="rId5" location="PerazaT2000" xr:uid="{CAE565D6-935E-4719-B867-D2AE21429A2E}"/>
+    <hyperlink ref="F1124" r:id="rId6" location="SinanogluE1986" xr:uid="{27841E86-CC24-4E45-84A8-043441D73FC1}"/>
+    <hyperlink ref="F1125" r:id="rId7" location="RodriguezG1952" xr:uid="{5E46BDBD-CA2D-4590-A2E0-DC599F650704}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87668FF1-17DD-45CA-AFC9-C996B64CF7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657878E5-E385-44C4-A9A3-6F91D0CBB6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="4107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4538" uniqueCount="4132">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12582,6 +12582,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezG1952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zonation base on planktonic foraminifera of Middle Miocene to Pliocene warm water sediments. </t>
+  </si>
+  <si>
+    <t>Bolli, H. H.; Bermúdez, P. J.</t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación de Geología, Minería y Petróleo, Volumen 8, Número 5, Mayo 1965.</t>
+  </si>
+  <si>
+    <t>A pollen diagram of the Pleistocene – Holocene boundary of Lake Valencia, Venezuela.</t>
+  </si>
+  <si>
+    <t>Review of Paleobotany and Palynology, Number 30,, pp. 297 – 312, 1980</t>
+  </si>
+  <si>
+    <t>Sedimentología y bioestratigrafía de alta resolución como herramienta para la caracterización del Flanco Norte del Campo El Furrial, Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sánchez, J.D.; Durán, I.; Cabrera, D. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arboles de Venezuela: Apamate y Barrabas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Fernández </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 64, Enero – Marzo de 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organización de una compañía petrolera. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W. B. Cleveland </t>
+  </si>
+  <si>
+    <t>Revista de la Universidad del Zulia, Aňo III, Número 9, Mayo – Agosto de 1952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bibliografía geológica de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comité Interfilial de Estratigrafía y Nomenclatura </t>
+  </si>
+  <si>
+    <t>Listado provisional del Código Geológico de Venezuela, 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barinas – Apure, Field Trip Guide </t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliHBermudezPJ1965</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SalgadoML1980</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SanchezJDetal2006</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#FernandezF1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#ClevelandWB1952</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#ComiteInterfilial1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/excursions.html#BPPDVSAWorkshop1992</t>
+  </si>
+  <si>
+    <t>PDVSA – BP Workshop, 27th August, 1992</t>
   </si>
 </sst>
 </file>
@@ -40150,7 +40225,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1125" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1132" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40181,7 +40256,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1127" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1132" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41002,38 +41077,175 @@
       </c>
     </row>
     <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1126">
+        <f t="shared" si="35"/>
+        <v>1125</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>4107</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>4108</v>
+      </c>
+      <c r="D1126">
+        <v>1965</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>4109</v>
+      </c>
       <c r="F1126" s="3" t="s">
-        <v>3931</v>
+        <v>4124</v>
+      </c>
+      <c r="G1126" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliHBermudezPJ1965</v>
       </c>
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1127">
+        <f t="shared" si="35"/>
+        <v>1126</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>4110</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>4070</v>
+      </c>
+      <c r="D1127">
+        <v>1980</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>4111</v>
+      </c>
       <c r="F1127" s="3" t="s">
-        <v>3931</v>
+        <v>4125</v>
+      </c>
+      <c r="G1127" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SalgadoML1980</v>
       </c>
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1128">
+        <f t="shared" si="35"/>
+        <v>1127</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>4112</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>4113</v>
+      </c>
+      <c r="D1128">
+        <v>2006</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>171</v>
+      </c>
       <c r="F1128" s="3" t="s">
-        <v>3931</v>
+        <v>4126</v>
+      </c>
+      <c r="G1128" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SanchezJDetal2006</v>
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1129">
+        <f t="shared" si="35"/>
+        <v>1128</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>4114</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>4115</v>
+      </c>
+      <c r="D1129">
+        <v>1993</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>4116</v>
+      </c>
       <c r="F1129" s="3" t="s">
-        <v>3931</v>
+        <v>4127</v>
+      </c>
+      <c r="G1129" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#FernandezF1993</v>
       </c>
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1130">
+        <f t="shared" si="35"/>
+        <v>1129</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>4117</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>4118</v>
+      </c>
+      <c r="D1130">
+        <v>1952</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>4119</v>
+      </c>
       <c r="F1130" s="3" t="s">
-        <v>3931</v>
+        <v>4128</v>
+      </c>
+      <c r="G1130" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#ClevelandWB1952</v>
       </c>
     </row>
     <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1131">
+        <f t="shared" si="35"/>
+        <v>1130</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>4120</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>4121</v>
+      </c>
+      <c r="D1131">
+        <v>1997</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>4122</v>
+      </c>
       <c r="F1131" s="3" t="s">
-        <v>3931</v>
+        <v>4129</v>
+      </c>
+      <c r="G1131" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#ComiteInterfilial1997</v>
       </c>
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1132">
+        <f t="shared" si="35"/>
+        <v>1131</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>4123</v>
+      </c>
+      <c r="D1132">
+        <v>1992</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>4131</v>
+      </c>
       <c r="F1132" s="3" t="s">
-        <v>3931</v>
+        <v>4130</v>
+      </c>
+      <c r="G1132" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/excursions.html#BPPDVSAWorkshop1992</v>
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
@@ -41222,8 +41434,15 @@
     <hyperlink ref="F1123" r:id="rId5" location="PerazaT2000" xr:uid="{CAE565D6-935E-4719-B867-D2AE21429A2E}"/>
     <hyperlink ref="F1124" r:id="rId6" location="SinanogluE1986" xr:uid="{27841E86-CC24-4E45-84A8-043441D73FC1}"/>
     <hyperlink ref="F1125" r:id="rId7" location="RodriguezG1952" xr:uid="{5E46BDBD-CA2D-4590-A2E0-DC599F650704}"/>
+    <hyperlink ref="F1126" r:id="rId8" location="BolliHBermudezPJ1965" xr:uid="{3800AB37-0602-4B95-BDED-44AE85139337}"/>
+    <hyperlink ref="F1127" r:id="rId9" location="SalgadoML1980" xr:uid="{131C3EA7-7418-47E2-A252-7B08F0DCBD83}"/>
+    <hyperlink ref="F1128" r:id="rId10" location="SanchezJDetal2006" xr:uid="{79E801B3-46C8-4005-A33F-9E81BEA0AF83}"/>
+    <hyperlink ref="F1129" r:id="rId11" location="FernandezF1993" xr:uid="{E3ABD571-63D8-4438-AA7A-E11139185D3D}"/>
+    <hyperlink ref="F1130" r:id="rId12" location="ClevelandWB1952" xr:uid="{464AC016-D1B7-4A89-BE36-31C538B271AB}"/>
+    <hyperlink ref="F1131" r:id="rId13" location="ComiteInterfilial1997" xr:uid="{8EBFB304-196D-4130-83DA-FE9C20E75BD5}"/>
+    <hyperlink ref="F1132" r:id="rId14" location="BPPDVSAWorkshop1992" xr:uid="{A9975020-9AC8-4620-8FA2-83F46E61A3F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657878E5-E385-44C4-A9A3-6F91D0CBB6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB57523-BC3F-4BB3-BC61-2EF119BA5B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4538" uniqueCount="4132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="4153">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12657,6 +12657,69 @@
   </si>
   <si>
     <t>PDVSA – BP Workshop, 27th August, 1992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El legado de Juan Emile Auguste Vogt (1929 – 2005). </t>
+  </si>
+  <si>
+    <t>Marine Environment and Nannofossils</t>
+  </si>
+  <si>
+    <t>Lambert, B</t>
+  </si>
+  <si>
+    <t>Apuntes del curso del Dr. Bernard Lambert, 1988.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loros, guacamayas y pericos. Aves amenazadas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lui, A.; Bigio, D.; Novo, I.; Rojas, F.; Albornoz, M.; Morales, L. G. </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 64, Enero – Marzo 1993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bioestratigrafía y distribución de biofacies en pozos del norte de la Faja Petrolífera del Orinoco. </t>
+  </si>
+  <si>
+    <t>Alejandro Euribe</t>
+  </si>
+  <si>
+    <t>Revista Técnica de Intevep, Número 1, pp. 37 – 46, Enero 1981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conceptos de Evolución. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Teresa Sánchez Benedetto </t>
+  </si>
+  <si>
+    <t>Universidad Central de Venezuela, Escuela de Geología, Guía de la profesora María Teresa Sánchez Benedetto, 1976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fósiles de Querales, Estado Falcón, Venezuela. </t>
+  </si>
+  <si>
+    <t>Recopilación realizada por Tulio Peraza para el Código Geológico de Venezuela. Trabajo Inédito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galería de fotografías históricas de las geociencias de Venezuela. </t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#LambertB1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#BigioLAetal1993</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#UribeA1981</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#Recopilacion2023</t>
   </si>
 </sst>
 </file>
@@ -13060,7 +13123,7 @@
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.5546875" style="4" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="55.21875" customWidth="1"/>
+    <col min="7" max="7" width="127.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -40225,7 +40288,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1132" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1139" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40256,7 +40319,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1132" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1139" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41249,101 +41312,238 @@
       </c>
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1133">
+        <f t="shared" si="35"/>
+        <v>1132</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>4132</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D1133">
+        <v>2025</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>3818</v>
+      </c>
       <c r="F1133" s="3" t="s">
-        <v>3931</v>
+        <v>4148</v>
+      </c>
+      <c r="G1133" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025</v>
       </c>
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1134">
+        <f t="shared" si="35"/>
+        <v>1133</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>4133</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>4134</v>
+      </c>
+      <c r="D1134">
+        <v>1988</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>4135</v>
+      </c>
       <c r="F1134" s="3" t="s">
-        <v>3931</v>
+        <v>4149</v>
+      </c>
+      <c r="G1134" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#LambertB1988</v>
       </c>
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1135">
+        <f t="shared" si="35"/>
+        <v>1134</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>4136</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>4137</v>
+      </c>
+      <c r="D1135">
+        <v>1993</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>4138</v>
+      </c>
       <c r="F1135" s="3" t="s">
-        <v>3931</v>
+        <v>4150</v>
+      </c>
+      <c r="G1135" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#BigioLAetal1993</v>
       </c>
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1136">
+        <f t="shared" si="35"/>
+        <v>1135</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>4139</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>4140</v>
+      </c>
+      <c r="D1136">
+        <v>1981</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>4141</v>
+      </c>
       <c r="F1136" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1137" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4151</v>
+      </c>
+      <c r="G1136" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#UribeA1981</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1137">
+        <f t="shared" si="35"/>
+        <v>1136</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>4142</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>4143</v>
+      </c>
+      <c r="D1137">
+        <v>1976</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>4144</v>
+      </c>
       <c r="F1137" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1138" spans="6:6" x14ac:dyDescent="0.3">
+        <v>3898</v>
+      </c>
+      <c r="G1137" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SanchezMT1976</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1138">
+        <f t="shared" si="35"/>
+        <v>1137</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>4145</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D1138">
+        <v>2000</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>4146</v>
+      </c>
       <c r="F1138" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1139" spans="6:6" x14ac:dyDescent="0.3">
+        <v>3925</v>
+      </c>
+      <c r="G1138" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2000</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1139">
+        <f t="shared" si="35"/>
+        <v>1138</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>4147</v>
+      </c>
+      <c r="D1139">
+        <v>2023</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>3700</v>
+      </c>
       <c r="F1139" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1140" spans="6:6" x14ac:dyDescent="0.3">
+        <v>4152</v>
+      </c>
+      <c r="G1139" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#Recopilacion2023</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1140" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1141" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1141" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1142" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1142" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1143" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1143" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1144" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1144" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1145" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1145" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1146" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1146" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1147" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1147" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1148" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1148" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1149" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1149" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1150" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1150" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1151" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1151" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1152" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1152" s="3" t="s">
         <v>3931</v>
       </c>
@@ -41441,8 +41641,15 @@
     <hyperlink ref="F1130" r:id="rId12" location="ClevelandWB1952" xr:uid="{464AC016-D1B7-4A89-BE36-31C538B271AB}"/>
     <hyperlink ref="F1131" r:id="rId13" location="ComiteInterfilial1997" xr:uid="{8EBFB304-196D-4130-83DA-FE9C20E75BD5}"/>
     <hyperlink ref="F1132" r:id="rId14" location="BPPDVSAWorkshop1992" xr:uid="{A9975020-9AC8-4620-8FA2-83F46E61A3F4}"/>
+    <hyperlink ref="F1133" r:id="rId15" location="RodriguezJA2025" xr:uid="{6DE1870D-8BE4-485C-A378-D1F63BC228CF}"/>
+    <hyperlink ref="F1134" r:id="rId16" location="LambertB1988" xr:uid="{7D32B93F-BE57-48BE-B7BA-BA6920B2928C}"/>
+    <hyperlink ref="F1135" r:id="rId17" location="BigioLAetal1993" xr:uid="{92059DF8-45AF-4BBC-A097-1CD750CAA464}"/>
+    <hyperlink ref="F1136" r:id="rId18" location="UribeA1981" xr:uid="{9D7B32BF-4DEB-48DA-9729-FA0E92FE567E}"/>
+    <hyperlink ref="F1137" r:id="rId19" location="SanchezMT1976" xr:uid="{E4801CCA-2A96-4A97-A08F-35273E989B5E}"/>
+    <hyperlink ref="F1138" r:id="rId20" location="PerazaT2000" xr:uid="{6DE53D6E-283A-4E5E-9DD4-6861E70C67B0}"/>
+    <hyperlink ref="F1139" r:id="rId21" location="Recopilacion2023" xr:uid="{33902BDD-8D74-4373-92E9-535EFAF7DD6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB57523-BC3F-4BB3-BC61-2EF119BA5B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDF193D-9318-4EDA-9EB5-1BF7A2644456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="4153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="4170">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12720,6 +12720,57 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#Recopilacion2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las visitas de H. M. Myers, W. B. Gilbert y R. H. Forbes a la Cueva de El Encantado, sureste de Caracas en 1867 y de Arthur CH. Hamilton- Gordon a la Cueva del Guácharo en 1870. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploring up-stream Rio Cachiri, Perija Mountains in 1945. </t>
+  </si>
+  <si>
+    <t>Peter Bitterli-Brunner</t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 65, Diciembre 1998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geochemical characterization of oceanographic and climatic changes recorded in Upper Albian to Lower Maastrichtian strata, western Venezuela. </t>
+  </si>
+  <si>
+    <t>Erlich, R.N.; Palmer-Koleman, S. E.; Lorente, M. A.</t>
+  </si>
+  <si>
+    <t>SEPM Research Conference, Paleogeography and Hydrocarbon. Potential of the La Luna Formation and related Cretaceous Anoxic Systems, 7th - 9th September 2000, Caracas, Venezuela</t>
+  </si>
+  <si>
+    <t>Algunos procesos de meteorización del Esquisto de Las Mercedes, estado Miranda, Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Abrisqueta, A.; Urbani, F.; Molina, D.; Díaz, D.; Angulo, F.; Bolívar, C.; Bezada, M. </t>
+  </si>
+  <si>
+    <t>Revista de la Facultad de Ingeniería, Universidad Central de Venezuela, Volumen 26, Número 3, pp. 55 – 62, 2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El calor de la tierra. Energía aprovechable </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Septiembre – Octubre 1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF2023</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#BitterliP1998</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/geochemistry.html#Erlichetal2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/igneous.html#DeAbrisquetaAetal2011</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1982</t>
   </si>
 </sst>
 </file>
@@ -40288,7 +40339,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1139" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1144" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40319,7 +40370,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1139" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1144" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41484,28 +41535,125 @@
       </c>
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1140">
+        <f t="shared" si="35"/>
+        <v>1139</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>4153</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>614</v>
+      </c>
+      <c r="D1140">
+        <v>2023</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>3700</v>
+      </c>
       <c r="F1140" s="3" t="s">
-        <v>3931</v>
+        <v>4165</v>
+      </c>
+      <c r="G1140" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF2023</v>
       </c>
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1141">
+        <f t="shared" si="35"/>
+        <v>1140</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>4154</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>4155</v>
+      </c>
+      <c r="D1141">
+        <v>1998</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>4156</v>
+      </c>
       <c r="F1141" s="3" t="s">
-        <v>3931</v>
+        <v>4166</v>
+      </c>
+      <c r="G1141" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#BitterliP1998</v>
       </c>
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1142">
+        <f t="shared" si="35"/>
+        <v>1141</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>4157</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>4158</v>
+      </c>
+      <c r="D1142">
+        <v>2000</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>4159</v>
+      </c>
       <c r="F1142" s="3" t="s">
-        <v>3931</v>
+        <v>4167</v>
+      </c>
+      <c r="G1142" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/geochemistry.html#Erlichetal2000</v>
       </c>
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1143">
+        <f t="shared" si="35"/>
+        <v>1142</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>4160</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>4161</v>
+      </c>
+      <c r="D1143">
+        <v>2011</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>4162</v>
+      </c>
       <c r="F1143" s="3" t="s">
-        <v>3931</v>
+        <v>4168</v>
+      </c>
+      <c r="G1143" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/igneous.html#DeAbrisquetaAetal2011</v>
       </c>
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1144">
+        <f t="shared" si="35"/>
+        <v>1143</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>4163</v>
+      </c>
+      <c r="D1144">
+        <v>1982</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>4164</v>
+      </c>
       <c r="F1144" s="3" t="s">
-        <v>3931</v>
+        <v>4169</v>
+      </c>
+      <c r="G1144" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1982</v>
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
@@ -41648,8 +41796,13 @@
     <hyperlink ref="F1137" r:id="rId19" location="SanchezMT1976" xr:uid="{E4801CCA-2A96-4A97-A08F-35273E989B5E}"/>
     <hyperlink ref="F1138" r:id="rId20" location="PerazaT2000" xr:uid="{6DE53D6E-283A-4E5E-9DD4-6861E70C67B0}"/>
     <hyperlink ref="F1139" r:id="rId21" location="Recopilacion2023" xr:uid="{33902BDD-8D74-4373-92E9-535EFAF7DD6A}"/>
+    <hyperlink ref="F1140" r:id="rId22" location="UrbaniF2023" xr:uid="{3B3744B4-7FE0-4875-A40B-3C469D82F30D}"/>
+    <hyperlink ref="F1141" r:id="rId23" location="BitterliP1998" xr:uid="{505228A0-864B-4A61-B830-E2C1C6B3998F}"/>
+    <hyperlink ref="F1142" r:id="rId24" location="Erlichetal2000" xr:uid="{CE5573BA-6B60-46DE-9430-FF4A9ABECA1E}"/>
+    <hyperlink ref="F1143" r:id="rId25" location="DeAbrisquetaAetal2011" xr:uid="{5586E65A-42D3-4D56-B2AD-1B6D879594FF}"/>
+    <hyperlink ref="F1144" r:id="rId26" location="Carta1982" xr:uid="{DA4BCDBB-6F87-4005-99B3-95A38A67EBFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDF193D-9318-4EDA-9EB5-1BF7A2644456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C74860-BF71-4B50-B4AF-7A8104590275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="4170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="4187">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12771,6 +12771,57 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#Carta1982</t>
+  </si>
+  <si>
+    <t>Arístides Rojas (1826 – 1894).</t>
+  </si>
+  <si>
+    <t>Pioneros en Venezuela, Código Geológico de Venezuela 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sismicidad histórica o sismología histórica, identidad y territorios. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late Pleistocene deglaciation histories in the central Merida Andes (Venezuela). </t>
+  </si>
+  <si>
+    <t>Isandra Fortuna Angel Ceballos</t>
+  </si>
+  <si>
+    <t>Tesis Doctoral presentada ante la ilustre Universidad Central de Venezuela por la Licenciada Isandra Fortuna Angel Ceballos, para optar al título de Doctor en Ciencias mención Geoquímica</t>
+  </si>
+  <si>
+    <t>Late Quaternary stratigraphy and sedimentation at site 1002, Cariaco Basin, Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peterson, L. C.; Haug, G. H.; Murray, R. W.; Yarinci, K. M.; King, J. W.; Bralower, T. J.; Kameo, K.; Rutherford, S. D.; Pearce, R. B. </t>
+  </si>
+  <si>
+    <t>Proceedings of the Ocean Drilling Program, Scientific Results, Vol. 165. 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemostratigraphic correlation of the source rock in the La Luna (K/T). Petroleum system in the southern Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briceňo, H.; Callejon, A. </t>
+  </si>
+  <si>
+    <t>SEPM Research Conference Paleogeography and Hydrocarbon Potential of the La Luna Formation and related Cretaceous Anoxic Systems. September 2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#Pioneros1997</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025f</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/glaciers.html#FortunaICeballosA2016</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#Petersonetal2000</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/geochemistry.html#BricenoHCallejonA2000</t>
   </si>
 </sst>
 </file>
@@ -12843,7 +12894,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -12851,6 +12902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -40339,7 +40391,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1144" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1149" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -40370,7 +40422,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1144" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1149" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41032,7 +41084,7 @@
       <c r="E1119" t="s">
         <v>4086</v>
       </c>
-      <c r="F1119" s="3" t="s">
+      <c r="F1119" s="5" t="s">
         <v>4101</v>
       </c>
       <c r="G1119" s="3" t="str">
@@ -41057,7 +41109,7 @@
       <c r="E1120" t="s">
         <v>151</v>
       </c>
-      <c r="F1120" s="3" t="s">
+      <c r="F1120" s="5" t="s">
         <v>4102</v>
       </c>
       <c r="G1120" s="3" t="str">
@@ -41082,7 +41134,7 @@
       <c r="E1121" t="s">
         <v>4091</v>
       </c>
-      <c r="F1121" s="3" t="s">
+      <c r="F1121" s="5" t="s">
         <v>4103</v>
       </c>
       <c r="G1121" s="3" t="str">
@@ -41107,7 +41159,7 @@
       <c r="E1122" t="s">
         <v>4094</v>
       </c>
-      <c r="F1122" s="3" t="s">
+      <c r="F1122" s="5" t="s">
         <v>4104</v>
       </c>
       <c r="G1122" s="3" t="str">
@@ -41132,7 +41184,7 @@
       <c r="E1123" t="s">
         <v>4096</v>
       </c>
-      <c r="F1123" s="3" t="s">
+      <c r="F1123" s="5" t="s">
         <v>3925</v>
       </c>
       <c r="G1123" s="3" t="str">
@@ -41157,7 +41209,7 @@
       <c r="E1124" t="s">
         <v>4098</v>
       </c>
-      <c r="F1124" s="3" t="s">
+      <c r="F1124" s="5" t="s">
         <v>4105</v>
       </c>
       <c r="G1124" s="3" t="str">
@@ -41182,7 +41234,7 @@
       <c r="E1125" t="s">
         <v>4048</v>
       </c>
-      <c r="F1125" s="3" t="s">
+      <c r="F1125" s="5" t="s">
         <v>4106</v>
       </c>
       <c r="G1125" s="3" t="str">
@@ -41207,7 +41259,7 @@
       <c r="E1126" t="s">
         <v>4109</v>
       </c>
-      <c r="F1126" s="3" t="s">
+      <c r="F1126" s="5" t="s">
         <v>4124</v>
       </c>
       <c r="G1126" s="3" t="str">
@@ -41232,7 +41284,7 @@
       <c r="E1127" t="s">
         <v>4111</v>
       </c>
-      <c r="F1127" s="3" t="s">
+      <c r="F1127" s="5" t="s">
         <v>4125</v>
       </c>
       <c r="G1127" s="3" t="str">
@@ -41257,7 +41309,7 @@
       <c r="E1128" t="s">
         <v>171</v>
       </c>
-      <c r="F1128" s="3" t="s">
+      <c r="F1128" s="5" t="s">
         <v>4126</v>
       </c>
       <c r="G1128" s="3" t="str">
@@ -41282,7 +41334,7 @@
       <c r="E1129" t="s">
         <v>4116</v>
       </c>
-      <c r="F1129" s="3" t="s">
+      <c r="F1129" s="5" t="s">
         <v>4127</v>
       </c>
       <c r="G1129" s="3" t="str">
@@ -41307,7 +41359,7 @@
       <c r="E1130" t="s">
         <v>4119</v>
       </c>
-      <c r="F1130" s="3" t="s">
+      <c r="F1130" s="5" t="s">
         <v>4128</v>
       </c>
       <c r="G1130" s="3" t="str">
@@ -41332,7 +41384,7 @@
       <c r="E1131" t="s">
         <v>4122</v>
       </c>
-      <c r="F1131" s="3" t="s">
+      <c r="F1131" s="5" t="s">
         <v>4129</v>
       </c>
       <c r="G1131" s="3" t="str">
@@ -41354,7 +41406,7 @@
       <c r="E1132" t="s">
         <v>4131</v>
       </c>
-      <c r="F1132" s="3" t="s">
+      <c r="F1132" s="5" t="s">
         <v>4130</v>
       </c>
       <c r="G1132" s="3" t="str">
@@ -41379,7 +41431,7 @@
       <c r="E1133" t="s">
         <v>3818</v>
       </c>
-      <c r="F1133" s="3" t="s">
+      <c r="F1133" s="5" t="s">
         <v>4148</v>
       </c>
       <c r="G1133" s="3" t="str">
@@ -41404,7 +41456,7 @@
       <c r="E1134" t="s">
         <v>4135</v>
       </c>
-      <c r="F1134" s="3" t="s">
+      <c r="F1134" s="5" t="s">
         <v>4149</v>
       </c>
       <c r="G1134" s="3" t="str">
@@ -41429,7 +41481,7 @@
       <c r="E1135" t="s">
         <v>4138</v>
       </c>
-      <c r="F1135" s="3" t="s">
+      <c r="F1135" s="5" t="s">
         <v>4150</v>
       </c>
       <c r="G1135" s="3" t="str">
@@ -41454,7 +41506,7 @@
       <c r="E1136" t="s">
         <v>4141</v>
       </c>
-      <c r="F1136" s="3" t="s">
+      <c r="F1136" s="5" t="s">
         <v>4151</v>
       </c>
       <c r="G1136" s="3" t="str">
@@ -41479,7 +41531,7 @@
       <c r="E1137" t="s">
         <v>4144</v>
       </c>
-      <c r="F1137" s="3" t="s">
+      <c r="F1137" s="5" t="s">
         <v>3898</v>
       </c>
       <c r="G1137" s="3" t="str">
@@ -41504,7 +41556,7 @@
       <c r="E1138" t="s">
         <v>4146</v>
       </c>
-      <c r="F1138" s="3" t="s">
+      <c r="F1138" s="5" t="s">
         <v>3925</v>
       </c>
       <c r="G1138" s="3" t="str">
@@ -41526,7 +41578,7 @@
       <c r="E1139" t="s">
         <v>3700</v>
       </c>
-      <c r="F1139" s="3" t="s">
+      <c r="F1139" s="5" t="s">
         <v>4152</v>
       </c>
       <c r="G1139" s="3" t="str">
@@ -41551,7 +41603,7 @@
       <c r="E1140" t="s">
         <v>3700</v>
       </c>
-      <c r="F1140" s="3" t="s">
+      <c r="F1140" s="5" t="s">
         <v>4165</v>
       </c>
       <c r="G1140" s="3" t="str">
@@ -41576,7 +41628,7 @@
       <c r="E1141" t="s">
         <v>4156</v>
       </c>
-      <c r="F1141" s="3" t="s">
+      <c r="F1141" s="5" t="s">
         <v>4166</v>
       </c>
       <c r="G1141" s="3" t="str">
@@ -41601,7 +41653,7 @@
       <c r="E1142" t="s">
         <v>4159</v>
       </c>
-      <c r="F1142" s="3" t="s">
+      <c r="F1142" s="5" t="s">
         <v>4167</v>
       </c>
       <c r="G1142" s="3" t="str">
@@ -41626,7 +41678,7 @@
       <c r="E1143" t="s">
         <v>4162</v>
       </c>
-      <c r="F1143" s="3" t="s">
+      <c r="F1143" s="5" t="s">
         <v>4168</v>
       </c>
       <c r="G1143" s="3" t="str">
@@ -41648,7 +41700,7 @@
       <c r="E1144" t="s">
         <v>4164</v>
       </c>
-      <c r="F1144" s="3" t="s">
+      <c r="F1144" s="5" t="s">
         <v>4169</v>
       </c>
       <c r="G1144" s="3" t="str">
@@ -41657,28 +41709,125 @@
       </c>
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1145" s="3" t="s">
-        <v>3931</v>
+      <c r="A1145">
+        <f t="shared" si="35"/>
+        <v>1144</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>4170</v>
+      </c>
+      <c r="D1145">
+        <v>1997</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>4171</v>
+      </c>
+      <c r="F1145" s="5" t="s">
+        <v>4182</v>
+      </c>
+      <c r="G1145" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#Pioneros1997</v>
       </c>
     </row>
     <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1146" s="3" t="s">
-        <v>3931</v>
+      <c r="A1146">
+        <f t="shared" si="35"/>
+        <v>1145</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>4172</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1146">
+        <v>2025</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>3242</v>
+      </c>
+      <c r="F1146" s="5" t="s">
+        <v>4183</v>
+      </c>
+      <c r="G1146" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025f</v>
       </c>
     </row>
     <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1147" s="3" t="s">
-        <v>3931</v>
+      <c r="A1147">
+        <f t="shared" si="35"/>
+        <v>1146</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>4173</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>4174</v>
+      </c>
+      <c r="D1147">
+        <v>2016</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>4175</v>
+      </c>
+      <c r="F1147" s="5" t="s">
+        <v>4184</v>
+      </c>
+      <c r="G1147" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/glaciers.html#FortunaICeballosA2016</v>
       </c>
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1148" s="3" t="s">
-        <v>3931</v>
+      <c r="A1148">
+        <f t="shared" si="35"/>
+        <v>1147</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>4176</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>4177</v>
+      </c>
+      <c r="D1148">
+        <v>2000</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>4178</v>
+      </c>
+      <c r="F1148" s="5" t="s">
+        <v>4185</v>
+      </c>
+      <c r="G1148" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#Petersonetal2000</v>
       </c>
     </row>
     <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1149" s="3" t="s">
-        <v>3931</v>
+      <c r="A1149">
+        <f t="shared" si="35"/>
+        <v>1148</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>4179</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>4180</v>
+      </c>
+      <c r="D1149">
+        <v>2000</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>4181</v>
+      </c>
+      <c r="F1149" s="5" t="s">
+        <v>4186</v>
+      </c>
+      <c r="G1149" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/geochemistry.html#BricenoHCallejonA2000</v>
       </c>
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
@@ -41774,35 +41923,7 @@
   </sheetData>
   <autoFilter ref="A1:G1167" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="F1119" r:id="rId1" location="CasasJE2024" xr:uid="{23A2EEBA-AA10-4E06-9AE1-D6206EC6DEF7}"/>
-    <hyperlink ref="F1120" r:id="rId2" location="BaqueroMetal2006" xr:uid="{C4B730AC-FFF1-47ED-A8CA-CD610C49980C}"/>
-    <hyperlink ref="F1121" r:id="rId3" location="WeissMPGoddardDA1974" xr:uid="{2DDCE41C-126B-4B19-8E0F-015B3CEB1FBB}"/>
-    <hyperlink ref="F1122" r:id="rId4" location="HunterVFBartokP1974" xr:uid="{5EDD6896-49FD-456E-87C5-8650DE3C0D4D}"/>
-    <hyperlink ref="F1123" r:id="rId5" location="PerazaT2000" xr:uid="{CAE565D6-935E-4719-B867-D2AE21429A2E}"/>
-    <hyperlink ref="F1124" r:id="rId6" location="SinanogluE1986" xr:uid="{27841E86-CC24-4E45-84A8-043441D73FC1}"/>
-    <hyperlink ref="F1125" r:id="rId7" location="RodriguezG1952" xr:uid="{5E46BDBD-CA2D-4590-A2E0-DC599F650704}"/>
-    <hyperlink ref="F1126" r:id="rId8" location="BolliHBermudezPJ1965" xr:uid="{3800AB37-0602-4B95-BDED-44AE85139337}"/>
-    <hyperlink ref="F1127" r:id="rId9" location="SalgadoML1980" xr:uid="{131C3EA7-7418-47E2-A252-7B08F0DCBD83}"/>
-    <hyperlink ref="F1128" r:id="rId10" location="SanchezJDetal2006" xr:uid="{79E801B3-46C8-4005-A33F-9E81BEA0AF83}"/>
-    <hyperlink ref="F1129" r:id="rId11" location="FernandezF1993" xr:uid="{E3ABD571-63D8-4438-AA7A-E11139185D3D}"/>
-    <hyperlink ref="F1130" r:id="rId12" location="ClevelandWB1952" xr:uid="{464AC016-D1B7-4A89-BE36-31C538B271AB}"/>
-    <hyperlink ref="F1131" r:id="rId13" location="ComiteInterfilial1997" xr:uid="{8EBFB304-196D-4130-83DA-FE9C20E75BD5}"/>
-    <hyperlink ref="F1132" r:id="rId14" location="BPPDVSAWorkshop1992" xr:uid="{A9975020-9AC8-4620-8FA2-83F46E61A3F4}"/>
-    <hyperlink ref="F1133" r:id="rId15" location="RodriguezJA2025" xr:uid="{6DE1870D-8BE4-485C-A378-D1F63BC228CF}"/>
-    <hyperlink ref="F1134" r:id="rId16" location="LambertB1988" xr:uid="{7D32B93F-BE57-48BE-B7BA-BA6920B2928C}"/>
-    <hyperlink ref="F1135" r:id="rId17" location="BigioLAetal1993" xr:uid="{92059DF8-45AF-4BBC-A097-1CD750CAA464}"/>
-    <hyperlink ref="F1136" r:id="rId18" location="UribeA1981" xr:uid="{9D7B32BF-4DEB-48DA-9729-FA0E92FE567E}"/>
-    <hyperlink ref="F1137" r:id="rId19" location="SanchezMT1976" xr:uid="{E4801CCA-2A96-4A97-A08F-35273E989B5E}"/>
-    <hyperlink ref="F1138" r:id="rId20" location="PerazaT2000" xr:uid="{6DE53D6E-283A-4E5E-9DD4-6861E70C67B0}"/>
-    <hyperlink ref="F1139" r:id="rId21" location="Recopilacion2023" xr:uid="{33902BDD-8D74-4373-92E9-535EFAF7DD6A}"/>
-    <hyperlink ref="F1140" r:id="rId22" location="UrbaniF2023" xr:uid="{3B3744B4-7FE0-4875-A40B-3C469D82F30D}"/>
-    <hyperlink ref="F1141" r:id="rId23" location="BitterliP1998" xr:uid="{505228A0-864B-4A61-B830-E2C1C6B3998F}"/>
-    <hyperlink ref="F1142" r:id="rId24" location="Erlichetal2000" xr:uid="{CE5573BA-6B60-46DE-9430-FF4A9ABECA1E}"/>
-    <hyperlink ref="F1143" r:id="rId25" location="DeAbrisquetaAetal2011" xr:uid="{5586E65A-42D3-4D56-B2AD-1B6D879594FF}"/>
-    <hyperlink ref="F1144" r:id="rId26" location="Carta1982" xr:uid="{DA4BCDBB-6F87-4005-99B3-95A38A67EBFE}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId27"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C74860-BF71-4B50-B4AF-7A8104590275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BBAC5-45F4-4E6A-AAFE-96ABCE5916E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4586" uniqueCount="4187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="4204">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12822,6 +12822,57 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/geochemistry.html#BricenoHCallejonA2000</t>
+  </si>
+  <si>
+    <t>Manual de foraminíferos de la Cuenca de Maracaibo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angel N. Fuenmayor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arboles emblemáticos de Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jesús Hoyos F. </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Edición Especial dedicada a la Semana de la Conservación, Sociedad Ciencias Naturales La Salle, 1982</t>
+  </si>
+  <si>
+    <t>Maraven S.A., División de Operaciones de Producción, Gerencia de Ingeniería de Petróleo, Gerencia de Geología, Maracaibo, Octubre de 1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situación actual y perspectivas de la industria de los minerales no metálicos en Venezuela. </t>
+  </si>
+  <si>
+    <t>IX Congreso Venezolano de Ingeniería, Maracaibo, Estado Zulia, Mayo 1974</t>
+  </si>
+  <si>
+    <t>Boletín de Historia de Las Geociencias en Venezuela, Número 90, pp. 3 – 14, Febrero 2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XVI Century salt production by aborigines in Quibor, Venezuela. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilhem Sievers (1860 – 1921). </t>
+  </si>
+  <si>
+    <t>Pioneros en Venezuela, Código Geológico de Venezuela, 2001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cuenca de Yaracuy: Una estructura Neotectónica en la región Centro – Occidental de Venezuela. </t>
+  </si>
+  <si>
+    <t>Geología Norandina, Número 8, Diciembre 1983</t>
+  </si>
+  <si>
+    <t>Revisión histórica y compilación de la fauna de Ammonites del Cretácico Tardío en Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulio Peraza </t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 80, Junio 2002</t>
   </si>
 </sst>
 </file>
@@ -12894,7 +12945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -12902,7 +12953,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -40422,7 +40472,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1149" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1156" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41084,7 +41134,7 @@
       <c r="E1119" t="s">
         <v>4086</v>
       </c>
-      <c r="F1119" s="5" t="s">
+      <c r="F1119" t="s">
         <v>4101</v>
       </c>
       <c r="G1119" s="3" t="str">
@@ -41109,7 +41159,7 @@
       <c r="E1120" t="s">
         <v>151</v>
       </c>
-      <c r="F1120" s="5" t="s">
+      <c r="F1120" t="s">
         <v>4102</v>
       </c>
       <c r="G1120" s="3" t="str">
@@ -41134,7 +41184,7 @@
       <c r="E1121" t="s">
         <v>4091</v>
       </c>
-      <c r="F1121" s="5" t="s">
+      <c r="F1121" t="s">
         <v>4103</v>
       </c>
       <c r="G1121" s="3" t="str">
@@ -41159,7 +41209,7 @@
       <c r="E1122" t="s">
         <v>4094</v>
       </c>
-      <c r="F1122" s="5" t="s">
+      <c r="F1122" t="s">
         <v>4104</v>
       </c>
       <c r="G1122" s="3" t="str">
@@ -41184,7 +41234,7 @@
       <c r="E1123" t="s">
         <v>4096</v>
       </c>
-      <c r="F1123" s="5" t="s">
+      <c r="F1123" t="s">
         <v>3925</v>
       </c>
       <c r="G1123" s="3" t="str">
@@ -41209,7 +41259,7 @@
       <c r="E1124" t="s">
         <v>4098</v>
       </c>
-      <c r="F1124" s="5" t="s">
+      <c r="F1124" t="s">
         <v>4105</v>
       </c>
       <c r="G1124" s="3" t="str">
@@ -41234,7 +41284,7 @@
       <c r="E1125" t="s">
         <v>4048</v>
       </c>
-      <c r="F1125" s="5" t="s">
+      <c r="F1125" t="s">
         <v>4106</v>
       </c>
       <c r="G1125" s="3" t="str">
@@ -41259,7 +41309,7 @@
       <c r="E1126" t="s">
         <v>4109</v>
       </c>
-      <c r="F1126" s="5" t="s">
+      <c r="F1126" t="s">
         <v>4124</v>
       </c>
       <c r="G1126" s="3" t="str">
@@ -41284,7 +41334,7 @@
       <c r="E1127" t="s">
         <v>4111</v>
       </c>
-      <c r="F1127" s="5" t="s">
+      <c r="F1127" t="s">
         <v>4125</v>
       </c>
       <c r="G1127" s="3" t="str">
@@ -41309,7 +41359,7 @@
       <c r="E1128" t="s">
         <v>171</v>
       </c>
-      <c r="F1128" s="5" t="s">
+      <c r="F1128" t="s">
         <v>4126</v>
       </c>
       <c r="G1128" s="3" t="str">
@@ -41334,7 +41384,7 @@
       <c r="E1129" t="s">
         <v>4116</v>
       </c>
-      <c r="F1129" s="5" t="s">
+      <c r="F1129" t="s">
         <v>4127</v>
       </c>
       <c r="G1129" s="3" t="str">
@@ -41359,7 +41409,7 @@
       <c r="E1130" t="s">
         <v>4119</v>
       </c>
-      <c r="F1130" s="5" t="s">
+      <c r="F1130" t="s">
         <v>4128</v>
       </c>
       <c r="G1130" s="3" t="str">
@@ -41384,7 +41434,7 @@
       <c r="E1131" t="s">
         <v>4122</v>
       </c>
-      <c r="F1131" s="5" t="s">
+      <c r="F1131" t="s">
         <v>4129</v>
       </c>
       <c r="G1131" s="3" t="str">
@@ -41406,7 +41456,7 @@
       <c r="E1132" t="s">
         <v>4131</v>
       </c>
-      <c r="F1132" s="5" t="s">
+      <c r="F1132" t="s">
         <v>4130</v>
       </c>
       <c r="G1132" s="3" t="str">
@@ -41431,7 +41481,7 @@
       <c r="E1133" t="s">
         <v>3818</v>
       </c>
-      <c r="F1133" s="5" t="s">
+      <c r="F1133" t="s">
         <v>4148</v>
       </c>
       <c r="G1133" s="3" t="str">
@@ -41456,7 +41506,7 @@
       <c r="E1134" t="s">
         <v>4135</v>
       </c>
-      <c r="F1134" s="5" t="s">
+      <c r="F1134" t="s">
         <v>4149</v>
       </c>
       <c r="G1134" s="3" t="str">
@@ -41481,7 +41531,7 @@
       <c r="E1135" t="s">
         <v>4138</v>
       </c>
-      <c r="F1135" s="5" t="s">
+      <c r="F1135" t="s">
         <v>4150</v>
       </c>
       <c r="G1135" s="3" t="str">
@@ -41506,7 +41556,7 @@
       <c r="E1136" t="s">
         <v>4141</v>
       </c>
-      <c r="F1136" s="5" t="s">
+      <c r="F1136" t="s">
         <v>4151</v>
       </c>
       <c r="G1136" s="3" t="str">
@@ -41531,7 +41581,7 @@
       <c r="E1137" t="s">
         <v>4144</v>
       </c>
-      <c r="F1137" s="5" t="s">
+      <c r="F1137" t="s">
         <v>3898</v>
       </c>
       <c r="G1137" s="3" t="str">
@@ -41556,7 +41606,7 @@
       <c r="E1138" t="s">
         <v>4146</v>
       </c>
-      <c r="F1138" s="5" t="s">
+      <c r="F1138" t="s">
         <v>3925</v>
       </c>
       <c r="G1138" s="3" t="str">
@@ -41578,7 +41628,7 @@
       <c r="E1139" t="s">
         <v>3700</v>
       </c>
-      <c r="F1139" s="5" t="s">
+      <c r="F1139" t="s">
         <v>4152</v>
       </c>
       <c r="G1139" s="3" t="str">
@@ -41603,7 +41653,7 @@
       <c r="E1140" t="s">
         <v>3700</v>
       </c>
-      <c r="F1140" s="5" t="s">
+      <c r="F1140" t="s">
         <v>4165</v>
       </c>
       <c r="G1140" s="3" t="str">
@@ -41628,7 +41678,7 @@
       <c r="E1141" t="s">
         <v>4156</v>
       </c>
-      <c r="F1141" s="5" t="s">
+      <c r="F1141" t="s">
         <v>4166</v>
       </c>
       <c r="G1141" s="3" t="str">
@@ -41653,7 +41703,7 @@
       <c r="E1142" t="s">
         <v>4159</v>
       </c>
-      <c r="F1142" s="5" t="s">
+      <c r="F1142" t="s">
         <v>4167</v>
       </c>
       <c r="G1142" s="3" t="str">
@@ -41678,7 +41728,7 @@
       <c r="E1143" t="s">
         <v>4162</v>
       </c>
-      <c r="F1143" s="5" t="s">
+      <c r="F1143" t="s">
         <v>4168</v>
       </c>
       <c r="G1143" s="3" t="str">
@@ -41700,7 +41750,7 @@
       <c r="E1144" t="s">
         <v>4164</v>
       </c>
-      <c r="F1144" s="5" t="s">
+      <c r="F1144" t="s">
         <v>4169</v>
       </c>
       <c r="G1144" s="3" t="str">
@@ -41722,7 +41772,7 @@
       <c r="E1145" t="s">
         <v>4171</v>
       </c>
-      <c r="F1145" s="5" t="s">
+      <c r="F1145" t="s">
         <v>4182</v>
       </c>
       <c r="G1145" s="3" t="str">
@@ -41747,7 +41797,7 @@
       <c r="E1146" t="s">
         <v>3242</v>
       </c>
-      <c r="F1146" s="5" t="s">
+      <c r="F1146" t="s">
         <v>4183</v>
       </c>
       <c r="G1146" s="3" t="str">
@@ -41772,7 +41822,7 @@
       <c r="E1147" t="s">
         <v>4175</v>
       </c>
-      <c r="F1147" s="5" t="s">
+      <c r="F1147" t="s">
         <v>4184</v>
       </c>
       <c r="G1147" s="3" t="str">
@@ -41797,7 +41847,7 @@
       <c r="E1148" t="s">
         <v>4178</v>
       </c>
-      <c r="F1148" s="5" t="s">
+      <c r="F1148" t="s">
         <v>4185</v>
       </c>
       <c r="G1148" s="3" t="str">
@@ -41822,7 +41872,7 @@
       <c r="E1149" t="s">
         <v>4181</v>
       </c>
-      <c r="F1149" s="5" t="s">
+      <c r="F1149" t="s">
         <v>4186</v>
       </c>
       <c r="G1149" s="3" t="str">
@@ -41831,91 +41881,203 @@
       </c>
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1150">
+        <f t="shared" si="35"/>
+        <v>1149</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>4187</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>4188</v>
+      </c>
+      <c r="D1150">
+        <v>1989</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>4192</v>
+      </c>
       <c r="F1150" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1151">
+        <f t="shared" si="35"/>
+        <v>1150</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>4189</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D1151">
+        <v>1982</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>4191</v>
+      </c>
       <c r="F1151" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1152">
+        <f t="shared" si="35"/>
+        <v>1151</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>4193</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>3237</v>
+      </c>
+      <c r="D1152">
+        <v>1974</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>4194</v>
+      </c>
       <c r="F1152" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1153" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1153">
+        <f t="shared" si="35"/>
+        <v>1152</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>4196</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>614</v>
+      </c>
+      <c r="D1153">
+        <v>2004</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>4195</v>
+      </c>
       <c r="F1153" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1154" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1154">
+        <f t="shared" si="35"/>
+        <v>1153</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>4197</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D1154">
+        <v>2001</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>4198</v>
+      </c>
       <c r="F1154" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1155" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1155">
+        <f t="shared" si="35"/>
+        <v>1154</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>4199</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D1155">
+        <v>1983</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>4200</v>
+      </c>
       <c r="F1155" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1156" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1156">
+        <f t="shared" si="35"/>
+        <v>1155</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>4201</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D1156">
+        <v>2002</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>4203</v>
+      </c>
       <c r="F1156" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1157" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1157" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1158" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1158" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1159" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1159" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1160" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1160" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1161" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1161" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1162" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1162" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1163" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1163" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1164" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1164" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1165" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1165" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1166" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1166" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1167" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F1167" s="3" t="s">
         <v>3931</v>
       </c>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BBAC5-45F4-4E6A-AAFE-96ABCE5916E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3395F948-8788-46B0-8B70-FFE2AE37190C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="4204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="4211">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12873,6 +12873,27 @@
   </si>
   <si>
     <t>Boletín de Historia de las Geociencias en Venezuela, Número 80, Junio 2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#FuenmayorA1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#HoyosJ1982</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#RodriguezSE1974</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#UrbaniF2004</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CGV2001</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#SchubertC1983</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2002</t>
   </si>
 </sst>
 </file>
@@ -12945,7 +12966,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -12953,6 +12974,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -40441,7 +40463,7 @@
         <v>4004</v>
       </c>
       <c r="G1091" s="3" t="str">
-        <f t="shared" ref="G1091:G1149" si="34">HYPERLINK(F1091)</f>
+        <f t="shared" ref="G1091:G1154" si="34">HYPERLINK(F1091)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#BolliH1985</v>
       </c>
     </row>
@@ -41897,8 +41919,12 @@
       <c r="E1150" t="s">
         <v>4192</v>
       </c>
-      <c r="F1150" s="3" t="s">
-        <v>3931</v>
+      <c r="F1150" s="5" t="s">
+        <v>4204</v>
+      </c>
+      <c r="G1150" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#FuenmayorA1989</v>
       </c>
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
@@ -41918,8 +41944,12 @@
       <c r="E1151" t="s">
         <v>4191</v>
       </c>
-      <c r="F1151" s="3" t="s">
-        <v>3931</v>
+      <c r="F1151" s="5" t="s">
+        <v>4205</v>
+      </c>
+      <c r="G1151" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#HoyosJ1982</v>
       </c>
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
@@ -41939,11 +41969,15 @@
       <c r="E1152" t="s">
         <v>4194</v>
       </c>
-      <c r="F1152" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1152" s="5" t="s">
+        <v>4206</v>
+      </c>
+      <c r="G1152" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#RodriguezSE1974</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1153">
         <f t="shared" si="35"/>
         <v>1152</v>
@@ -41960,11 +41994,15 @@
       <c r="E1153" t="s">
         <v>4195</v>
       </c>
-      <c r="F1153" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1153" s="5" t="s">
+        <v>4207</v>
+      </c>
+      <c r="G1153" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#UrbaniF2004</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1154">
         <f t="shared" si="35"/>
         <v>1153</v>
@@ -41981,11 +42019,15 @@
       <c r="E1154" t="s">
         <v>4198</v>
       </c>
-      <c r="F1154" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1154" s="5" t="s">
+        <v>4208</v>
+      </c>
+      <c r="G1154" s="3" t="str">
+        <f t="shared" si="34"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#CGV2001</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1155">
         <f t="shared" si="35"/>
         <v>1154</v>
@@ -42002,11 +42044,15 @@
       <c r="E1155" t="s">
         <v>4200</v>
       </c>
-      <c r="F1155" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1155" s="5" t="s">
+        <v>4209</v>
+      </c>
+      <c r="G1155" s="3" t="str">
+        <f t="shared" ref="G1155:G1156" si="36">HYPERLINK(F1155)</f>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#SchubertC1983</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1156">
         <f t="shared" si="35"/>
         <v>1155</v>
@@ -42023,61 +42069,65 @@
       <c r="E1156" t="s">
         <v>4203</v>
       </c>
-      <c r="F1156" s="3" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="1157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1156" s="5" t="s">
+        <v>4210</v>
+      </c>
+      <c r="G1156" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2002</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1157" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1158" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1159" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1160" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1161" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1162" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1163" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1164" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1165" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1166" s="3" t="s">
         <v>3931</v>
       </c>
     </row>
-    <row r="1167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1167" s="3" t="s">
         <v>3931</v>
       </c>

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3395F948-8788-46B0-8B70-FFE2AE37190C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713F82D7-C58B-4241-A7B4-F7606C6C9AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="4211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="4236">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12894,6 +12894,81 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2002</t>
+  </si>
+  <si>
+    <t>El ambiente tectónico de formación del depósito de sulfuro masivo de Lima II y las mineralizaciones asociadas, Bailadores, Estado Mérida, Cordillera de Mérida, Venezuela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramón S. Sifontes </t>
+  </si>
+  <si>
+    <t>Boletín de la Sociedad Venezolana de Geólogos, Volumen 26, Número 1, pp. 36-56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Cretaceous marine vertebrate assemblages from north – western Venezuela and their significance. </t>
+  </si>
+  <si>
+    <t>Moody, J.M.; Maisey, J.G.</t>
+  </si>
+  <si>
+    <t>Journal of Vertebrate Paleontology, 14 (1), pp. 1 – 8, March 1994.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reporte de Karl Gerhardt 1897, sobre una fauna de Ammonites en el Estado Táchira, Venezuela. </t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 80, pp. 3-9, Junio 2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métodos de preparación de muestras de nannoplancton calcáreo. </t>
+  </si>
+  <si>
+    <t>Lagoven S.A., Estudios Regionales, Laboratorio de Geología, 1989</t>
+  </si>
+  <si>
+    <t>Juan Manuel Cajigal y Odoardo Barcelona (Estado Anzoátegui) 10 / 8/ 1803 – Yaguaraparo (Estado Sucre) 10 / 2 / 1856.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elke Nieschulz de Stockhausen </t>
+  </si>
+  <si>
+    <t>Boletín de la Academia Nacional de la Ingenierňa y el Hábitat, Número 48, pp. 146 – 148, Septiembre 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geometría y Litofacies del Cretácico de la Cuenca de Maracaibo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savian, V. y Scherer, W. </t>
+  </si>
+  <si>
+    <t>Poster de Vania Savian y Wolfgang Scherer, Intevep 1997</t>
+  </si>
+  <si>
+    <t>El Conde Adolfo Mestiatis (1860 – 1935).</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#SifontesRS2001</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MoodyJMMaiseyJG1994</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2002a</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CastroM1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#NieschulzE</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SavainVSchererW1997</t>
+  </si>
+  <si>
+    <t>Boletín de Historia de las Geociencias en Venezuela, Número 57, pp1 – 17, Abril 1996</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF1996</t>
   </si>
 </sst>
 </file>
@@ -40494,7 +40569,7 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093">
-        <f t="shared" ref="A1093:A1156" si="35">A1092+1</f>
+        <f t="shared" ref="A1093:A1157" si="35">A1092+1</f>
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
@@ -41919,7 +41994,7 @@
       <c r="E1150" t="s">
         <v>4192</v>
       </c>
-      <c r="F1150" s="5" t="s">
+      <c r="F1150" t="s">
         <v>4204</v>
       </c>
       <c r="G1150" s="3" t="str">
@@ -41944,7 +42019,7 @@
       <c r="E1151" t="s">
         <v>4191</v>
       </c>
-      <c r="F1151" s="5" t="s">
+      <c r="F1151" t="s">
         <v>4205</v>
       </c>
       <c r="G1151" s="3" t="str">
@@ -41969,7 +42044,7 @@
       <c r="E1152" t="s">
         <v>4194</v>
       </c>
-      <c r="F1152" s="5" t="s">
+      <c r="F1152" t="s">
         <v>4206</v>
       </c>
       <c r="G1152" s="3" t="str">
@@ -41994,7 +42069,7 @@
       <c r="E1153" t="s">
         <v>4195</v>
       </c>
-      <c r="F1153" s="5" t="s">
+      <c r="F1153" t="s">
         <v>4207</v>
       </c>
       <c r="G1153" s="3" t="str">
@@ -42019,7 +42094,7 @@
       <c r="E1154" t="s">
         <v>4198</v>
       </c>
-      <c r="F1154" s="5" t="s">
+      <c r="F1154" t="s">
         <v>4208</v>
       </c>
       <c r="G1154" s="3" t="str">
@@ -42044,11 +42119,11 @@
       <c r="E1155" t="s">
         <v>4200</v>
       </c>
-      <c r="F1155" s="5" t="s">
+      <c r="F1155" t="s">
         <v>4209</v>
       </c>
       <c r="G1155" s="3" t="str">
-        <f t="shared" ref="G1155:G1156" si="36">HYPERLINK(F1155)</f>
+        <f t="shared" ref="G1155:G1163" si="36">HYPERLINK(F1155)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#SchubertC1983</v>
       </c>
     </row>
@@ -42069,7 +42144,7 @@
       <c r="E1156" t="s">
         <v>4203</v>
       </c>
-      <c r="F1156" s="5" t="s">
+      <c r="F1156" t="s">
         <v>4210</v>
       </c>
       <c r="G1156" s="3" t="str">
@@ -42078,38 +42153,178 @@
       </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1157" s="3" t="s">
-        <v>3931</v>
+      <c r="A1157">
+        <f t="shared" si="35"/>
+        <v>1156</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>4211</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>4212</v>
+      </c>
+      <c r="D1157">
+        <v>2001</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>4213</v>
+      </c>
+      <c r="F1157" s="5" t="s">
+        <v>4228</v>
+      </c>
+      <c r="G1157" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#SifontesRS2001</v>
       </c>
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1158" s="3" t="s">
-        <v>3931</v>
+      <c r="A1158">
+        <f t="shared" ref="A1158:A1163" si="37">A1157+1</f>
+        <v>1157</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>4214</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>4215</v>
+      </c>
+      <c r="D1158">
+        <v>1994</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>4216</v>
+      </c>
+      <c r="F1158" s="5" t="s">
+        <v>4229</v>
+      </c>
+      <c r="G1158" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MoodyJMMaiseyJG1994</v>
       </c>
     </row>
     <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1159" s="3" t="s">
-        <v>3931</v>
+      <c r="A1159">
+        <f t="shared" si="37"/>
+        <v>1158</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>4217</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>4202</v>
+      </c>
+      <c r="D1159">
+        <v>2002</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>4218</v>
+      </c>
+      <c r="F1159" s="5" t="s">
+        <v>4230</v>
+      </c>
+      <c r="G1159" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#PerazaT2002a</v>
       </c>
     </row>
     <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1160" s="3" t="s">
-        <v>3931</v>
+      <c r="A1160">
+        <f t="shared" si="37"/>
+        <v>1159</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>4219</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1160">
+        <v>1989</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>4220</v>
+      </c>
+      <c r="F1160" s="5" t="s">
+        <v>4231</v>
+      </c>
+      <c r="G1160" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#CastroM1989</v>
       </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1161" s="3" t="s">
-        <v>3931</v>
+      <c r="A1161">
+        <f t="shared" si="37"/>
+        <v>1160</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>4221</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>4222</v>
+      </c>
+      <c r="D1161">
+        <v>2013</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>4223</v>
+      </c>
+      <c r="F1161" s="5" t="s">
+        <v>4232</v>
+      </c>
+      <c r="G1161" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#NieschulzE</v>
       </c>
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1162" s="3" t="s">
-        <v>3931</v>
+      <c r="A1162">
+        <f t="shared" si="37"/>
+        <v>1161</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>4224</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>4225</v>
+      </c>
+      <c r="D1162">
+        <v>1997</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>4226</v>
+      </c>
+      <c r="F1162" s="5" t="s">
+        <v>4233</v>
+      </c>
+      <c r="G1162" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#SavainVSchererW1997</v>
       </c>
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1163" s="3" t="s">
-        <v>3931</v>
+      <c r="A1163">
+        <f t="shared" si="37"/>
+        <v>1162</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>4227</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D1163">
+        <v>1996</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>4234</v>
+      </c>
+      <c r="F1163" s="5" t="s">
+        <v>4235</v>
+      </c>
+      <c r="G1163" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF1996</v>
       </c>
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.3">

--- a/NotasGeologiaPublicationList.xlsx
+++ b/NotasGeologiaPublicationList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\Notas-Geologicas-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713F82D7-C58B-4241-A7B4-F7606C6C9AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C7445B-B8AB-4654-8503-63D179F7EFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="4236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4652" uniqueCount="4261">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -12056,9 +12056,6 @@
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/speleology.html#CarrenoR2024</t>
   </si>
   <si>
-    <t>https://mariantoc.github.io/Notas-Geologicas-2025/</t>
-  </si>
-  <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2025d</t>
   </si>
   <si>
@@ -12969,6 +12966,107 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#UrbaniF1996</t>
+  </si>
+  <si>
+    <t>New data on Venezuela rock art.</t>
+  </si>
+  <si>
+    <t>Karolina Juszczyk y Stanislaw Rzeznik</t>
+  </si>
+  <si>
+    <t>Rock Art Research, Volume 43, Number 1</t>
+  </si>
+  <si>
+    <t>El petróleo venezolano en los mercados mundiales.</t>
+  </si>
+  <si>
+    <t>E. Sugar</t>
+  </si>
+  <si>
+    <t>Boletín informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 2, Número 8, Agosto 1954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcillas blancas en el Estado Lara. </t>
+  </si>
+  <si>
+    <t>Dionisio Zozaya</t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 15, Número 7, 8 y 9, Julio, Agosto y Septiembre de 1972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Determinación de zonas de optima permeabilidad en el yacimiento Laguna de Post-Eoceno, Cuenca del Lago de Maracaibo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gonzalo Gamero </t>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volúmen 16, Números 1, 2 y 3, Enero, Febrero y Marzo de 1973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sergio Foghin – Pillin, un singular personaje de la geografía venezolana. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Agosto 2023</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Zonación del Post – Eoceno de la Paleoprovincia Caribe – Antillana a base de la taxa de </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Turritella</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Molusco: Gasterópodo). </t>
+    </r>
+  </si>
+  <si>
+    <t>Boletín Informativo de la Asociación Venezolana de Geología, Minería y Petróleo, Volumen 14, Número 2, Febrero 1971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Aves: Un ecosistema para conservar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Carlos Jácome </t>
+  </si>
+  <si>
+    <t>Carta Ecológica de Lagoven S.A., Número 37, Julio – Agosto de 1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#JuszcykKRzenik202S6</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/fields.html#SugarE1954</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#ZosayaD1972</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GameroG1973</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2023</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MacsotayO1971</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#JacomeJC1987</t>
   </si>
 </sst>
 </file>
@@ -13041,7 +13139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -13049,7 +13147,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -13365,7 +13462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}">
-  <dimension ref="A1:H1167"/>
+  <dimension ref="A1:H1170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="66.5546875" customWidth="1"/>
@@ -40110,7 +40207,7 @@
         <v>3774</v>
       </c>
       <c r="F1074" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="G1074" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40148,19 +40245,19 @@
         <v>1075</v>
       </c>
       <c r="B1076" t="s">
+        <v>3932</v>
+      </c>
+      <c r="C1076" t="s">
         <v>3933</v>
-      </c>
-      <c r="C1076" t="s">
-        <v>3934</v>
       </c>
       <c r="D1076">
         <v>2024</v>
       </c>
       <c r="E1076" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="F1076" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="G1076" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40173,19 +40270,19 @@
         <v>1076</v>
       </c>
       <c r="B1077" t="s">
+        <v>3935</v>
+      </c>
+      <c r="C1077" t="s">
         <v>3936</v>
-      </c>
-      <c r="C1077" t="s">
-        <v>3937</v>
       </c>
       <c r="D1077">
         <v>2024</v>
       </c>
       <c r="E1077" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="F1077" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="G1077" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40198,10 +40295,10 @@
         <v>1077</v>
       </c>
       <c r="B1078" t="s">
+        <v>3937</v>
+      </c>
+      <c r="C1078" t="s">
         <v>3938</v>
-      </c>
-      <c r="C1078" t="s">
-        <v>3939</v>
       </c>
       <c r="D1078">
         <v>2006</v>
@@ -40210,7 +40307,7 @@
         <v>151</v>
       </c>
       <c r="F1078" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="G1078" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40223,19 +40320,19 @@
         <v>1078</v>
       </c>
       <c r="B1079" t="s">
+        <v>3939</v>
+      </c>
+      <c r="C1079" t="s">
         <v>3940</v>
-      </c>
-      <c r="C1079" t="s">
-        <v>3941</v>
       </c>
       <c r="D1079">
         <v>1995</v>
       </c>
       <c r="E1079" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
       <c r="F1079" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="G1079" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40248,19 +40345,19 @@
         <v>1079</v>
       </c>
       <c r="B1080" t="s">
+        <v>3942</v>
+      </c>
+      <c r="C1080" t="s">
         <v>3943</v>
-      </c>
-      <c r="C1080" t="s">
-        <v>3944</v>
       </c>
       <c r="D1080">
         <v>1990</v>
       </c>
       <c r="E1080" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
       <c r="F1080" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="G1080" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40273,19 +40370,19 @@
         <v>1080</v>
       </c>
       <c r="B1081" t="s">
+        <v>3945</v>
+      </c>
+      <c r="C1081" t="s">
         <v>3946</v>
-      </c>
-      <c r="C1081" t="s">
-        <v>3947</v>
       </c>
       <c r="D1081">
         <v>1975</v>
       </c>
       <c r="E1081" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="F1081" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="G1081" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40298,19 +40395,19 @@
         <v>1081</v>
       </c>
       <c r="B1082" t="s">
+        <v>3948</v>
+      </c>
+      <c r="C1082" t="s">
         <v>3949</v>
-      </c>
-      <c r="C1082" t="s">
-        <v>3950</v>
       </c>
       <c r="D1082">
         <v>1992</v>
       </c>
       <c r="E1082" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="F1082" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="G1082" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40323,7 +40420,7 @@
         <v>1082</v>
       </c>
       <c r="B1083" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="C1083" t="s">
         <v>22</v>
@@ -40332,10 +40429,10 @@
         <v>2025</v>
       </c>
       <c r="E1083" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="F1083" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="G1083" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40348,19 +40445,19 @@
         <v>1083</v>
       </c>
       <c r="B1084" t="s">
+        <v>3960</v>
+      </c>
+      <c r="C1084" t="s">
         <v>3961</v>
-      </c>
-      <c r="C1084" t="s">
-        <v>3962</v>
       </c>
       <c r="D1084">
         <v>2016</v>
       </c>
       <c r="E1084" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="F1084" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="G1084" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40373,10 +40470,10 @@
         <v>1084</v>
       </c>
       <c r="B1085" t="s">
+        <v>3963</v>
+      </c>
+      <c r="C1085" t="s">
         <v>3964</v>
-      </c>
-      <c r="C1085" t="s">
-        <v>3965</v>
       </c>
       <c r="D1085">
         <v>2025</v>
@@ -40385,7 +40482,7 @@
         <v>3818</v>
       </c>
       <c r="F1085" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="G1085" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40398,19 +40495,19 @@
         <v>1085</v>
       </c>
       <c r="B1086" t="s">
+        <v>3965</v>
+      </c>
+      <c r="C1086" t="s">
         <v>3966</v>
-      </c>
-      <c r="C1086" t="s">
-        <v>3967</v>
       </c>
       <c r="D1086">
         <v>1998</v>
       </c>
       <c r="E1086" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="F1086" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
       <c r="G1086" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40423,19 +40520,19 @@
         <v>1086</v>
       </c>
       <c r="B1087" t="s">
+        <v>3968</v>
+      </c>
+      <c r="C1087" t="s">
         <v>3969</v>
-      </c>
-      <c r="C1087" t="s">
-        <v>3970</v>
       </c>
       <c r="D1087">
         <v>1993</v>
       </c>
       <c r="E1087" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="F1087" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="G1087" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40448,19 +40545,19 @@
         <v>1087</v>
       </c>
       <c r="B1088" t="s">
+        <v>3971</v>
+      </c>
+      <c r="C1088" t="s">
         <v>3972</v>
-      </c>
-      <c r="C1088" t="s">
-        <v>3973</v>
       </c>
       <c r="D1088">
         <v>1991</v>
       </c>
       <c r="E1088" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="F1088" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="G1088" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40473,10 +40570,10 @@
         <v>1088</v>
       </c>
       <c r="B1089" t="s">
+        <v>3974</v>
+      </c>
+      <c r="C1089" t="s">
         <v>3975</v>
-      </c>
-      <c r="C1089" t="s">
-        <v>3976</v>
       </c>
       <c r="D1089">
         <v>2006</v>
@@ -40485,7 +40582,7 @@
         <v>151</v>
       </c>
       <c r="F1089" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="G1089" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40498,19 +40595,19 @@
         <v>1089</v>
       </c>
       <c r="B1090" t="s">
+        <v>3983</v>
+      </c>
+      <c r="C1090" t="s">
         <v>3984</v>
-      </c>
-      <c r="C1090" t="s">
-        <v>3985</v>
       </c>
       <c r="D1090">
         <v>1985</v>
       </c>
       <c r="E1090" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="F1090" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="G1090" s="3" t="str">
         <f t="shared" si="32"/>
@@ -40523,19 +40620,19 @@
         <v>1090</v>
       </c>
       <c r="B1091" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
       <c r="C1091" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
       <c r="D1091">
         <v>1985</v>
       </c>
       <c r="E1091" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
       <c r="F1091" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="G1091" s="3" t="str">
         <f t="shared" ref="G1091:G1154" si="34">HYPERLINK(F1091)</f>
@@ -40548,19 +40645,19 @@
         <v>1091</v>
       </c>
       <c r="B1092" t="s">
+        <v>3987</v>
+      </c>
+      <c r="C1092" t="s">
         <v>3988</v>
-      </c>
-      <c r="C1092" t="s">
-        <v>3989</v>
       </c>
       <c r="D1092">
         <v>1971</v>
       </c>
       <c r="E1092" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
       <c r="F1092" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="G1092" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40573,19 +40670,19 @@
         <v>1092</v>
       </c>
       <c r="B1093" t="s">
+        <v>3990</v>
+      </c>
+      <c r="C1093" t="s">
         <v>3991</v>
-      </c>
-      <c r="C1093" t="s">
-        <v>3992</v>
       </c>
       <c r="D1093">
         <v>1991</v>
       </c>
       <c r="E1093" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="F1093" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="G1093" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40598,19 +40695,19 @@
         <v>1093</v>
       </c>
       <c r="B1094" t="s">
+        <v>3993</v>
+      </c>
+      <c r="C1094" t="s">
         <v>3994</v>
-      </c>
-      <c r="C1094" t="s">
-        <v>3995</v>
       </c>
       <c r="D1094">
         <v>1986</v>
       </c>
       <c r="E1094" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="F1094" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="G1094" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40623,19 +40720,19 @@
         <v>1094</v>
       </c>
       <c r="B1095" t="s">
+        <v>3996</v>
+      </c>
+      <c r="C1095" t="s">
         <v>3997</v>
-      </c>
-      <c r="C1095" t="s">
-        <v>3998</v>
       </c>
       <c r="D1095">
         <v>1989</v>
       </c>
       <c r="E1095" t="s">
-        <v>3999</v>
+        <v>3998</v>
       </c>
       <c r="F1095" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="G1095" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40648,19 +40745,19 @@
         <v>1095</v>
       </c>
       <c r="B1096" t="s">
+        <v>3999</v>
+      </c>
+      <c r="C1096" t="s">
         <v>4000</v>
-      </c>
-      <c r="C1096" t="s">
-        <v>4001</v>
       </c>
       <c r="D1096">
         <v>2025</v>
       </c>
       <c r="E1096" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="F1096" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="G1096" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40673,7 +40770,7 @@
         <v>1096</v>
       </c>
       <c r="B1097" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C1097" t="s">
         <v>220</v>
@@ -40682,10 +40779,10 @@
         <v>2005</v>
       </c>
       <c r="E1097" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="F1097" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="G1097" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40698,19 +40795,19 @@
         <v>1097</v>
       </c>
       <c r="B1098" t="s">
+        <v>4011</v>
+      </c>
+      <c r="C1098" t="s">
         <v>4012</v>
-      </c>
-      <c r="C1098" t="s">
-        <v>4013</v>
       </c>
       <c r="D1098">
         <v>1997</v>
       </c>
       <c r="E1098" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="F1098" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="G1098" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40723,10 +40820,10 @@
         <v>1098</v>
       </c>
       <c r="B1099" t="s">
+        <v>4014</v>
+      </c>
+      <c r="C1099" t="s">
         <v>4015</v>
-      </c>
-      <c r="C1099" t="s">
-        <v>4016</v>
       </c>
       <c r="D1099">
         <v>1990</v>
@@ -40735,7 +40832,7 @@
         <v>3859</v>
       </c>
       <c r="F1099" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="G1099" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40748,19 +40845,19 @@
         <v>1099</v>
       </c>
       <c r="B1100" t="s">
+        <v>4016</v>
+      </c>
+      <c r="C1100" t="s">
         <v>4017</v>
-      </c>
-      <c r="C1100" t="s">
-        <v>4018</v>
       </c>
       <c r="D1100">
         <v>1982</v>
       </c>
       <c r="E1100" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="F1100" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="G1100" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40773,19 +40870,19 @@
         <v>1100</v>
       </c>
       <c r="B1101" t="s">
+        <v>4019</v>
+      </c>
+      <c r="C1101" t="s">
         <v>4020</v>
-      </c>
-      <c r="C1101" t="s">
-        <v>4021</v>
       </c>
       <c r="D1101">
         <v>2000</v>
       </c>
       <c r="E1101" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1101" t="s">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="G1101" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40798,19 +40895,19 @@
         <v>1101</v>
       </c>
       <c r="B1102" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C1102" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="D1102">
         <v>2003</v>
       </c>
       <c r="E1102" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="F1102" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="G1102" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40823,16 +40920,16 @@
         <v>1102</v>
       </c>
       <c r="B1103" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D1103">
         <v>1990</v>
       </c>
       <c r="E1103" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="F1103" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="G1103" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40845,19 +40942,19 @@
         <v>1103</v>
       </c>
       <c r="B1104" t="s">
+        <v>4026</v>
+      </c>
+      <c r="C1104" t="s">
         <v>4027</v>
-      </c>
-      <c r="C1104" t="s">
-        <v>4028</v>
       </c>
       <c r="D1104">
         <v>1997</v>
       </c>
       <c r="E1104" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="F1104" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="G1104" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40870,7 +40967,7 @@
         <v>1104</v>
       </c>
       <c r="B1105" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="C1105" t="s">
         <v>2861</v>
@@ -40879,10 +40976,10 @@
         <v>1997</v>
       </c>
       <c r="E1105" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="F1105" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="G1105" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40895,7 +40992,7 @@
         <v>1105</v>
       </c>
       <c r="B1106" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="C1106" t="s">
         <v>3306</v>
@@ -40904,10 +41001,10 @@
         <v>2025</v>
       </c>
       <c r="E1106" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="F1106" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="G1106" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40920,19 +41017,19 @@
         <v>1106</v>
       </c>
       <c r="B1107" t="s">
+        <v>4040</v>
+      </c>
+      <c r="C1107" t="s">
         <v>4041</v>
-      </c>
-      <c r="C1107" t="s">
-        <v>4042</v>
       </c>
       <c r="D1107">
         <v>2000</v>
       </c>
       <c r="E1107" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="F1107" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="G1107" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40945,10 +41042,10 @@
         <v>1107</v>
       </c>
       <c r="B1108" t="s">
+        <v>4043</v>
+      </c>
+      <c r="C1108" t="s">
         <v>4044</v>
-      </c>
-      <c r="C1108" t="s">
-        <v>4045</v>
       </c>
       <c r="D1108">
         <v>1990</v>
@@ -40957,7 +41054,7 @@
         <v>3859</v>
       </c>
       <c r="F1108" t="s">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="G1108" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40970,19 +41067,19 @@
         <v>1108</v>
       </c>
       <c r="B1109" t="s">
+        <v>4045</v>
+      </c>
+      <c r="C1109" t="s">
         <v>4046</v>
-      </c>
-      <c r="C1109" t="s">
-        <v>4047</v>
       </c>
       <c r="D1109">
         <v>1952</v>
       </c>
       <c r="E1109" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="F1109" t="s">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="G1109" s="3" t="str">
         <f t="shared" si="34"/>
@@ -40995,19 +41092,19 @@
         <v>1109</v>
       </c>
       <c r="B1110" t="s">
+        <v>4048</v>
+      </c>
+      <c r="C1110" t="s">
         <v>4049</v>
-      </c>
-      <c r="C1110" t="s">
-        <v>4050</v>
       </c>
       <c r="D1110">
         <v>1992</v>
       </c>
       <c r="E1110" t="s">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="F1110" t="s">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="G1110" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41020,19 +41117,19 @@
         <v>1110</v>
       </c>
       <c r="B1111" t="s">
+        <v>4051</v>
+      </c>
+      <c r="C1111" t="s">
         <v>4052</v>
-      </c>
-      <c r="C1111" t="s">
-        <v>4053</v>
       </c>
       <c r="D1111">
         <v>1993</v>
       </c>
       <c r="E1111" t="s">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="F1111" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="G1111" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41045,7 +41142,7 @@
         <v>1111</v>
       </c>
       <c r="B1112" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="C1112" t="s">
         <v>2861</v>
@@ -41054,10 +41151,10 @@
         <v>1997</v>
       </c>
       <c r="E1112" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="F1112" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="G1112" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41070,10 +41167,10 @@
         <v>1112</v>
       </c>
       <c r="B1113" t="s">
+        <v>4055</v>
+      </c>
+      <c r="C1113" t="s">
         <v>4056</v>
-      </c>
-      <c r="C1113" t="s">
-        <v>4057</v>
       </c>
       <c r="D1113">
         <v>1990</v>
@@ -41082,7 +41179,7 @@
         <v>3859</v>
       </c>
       <c r="F1113" t="s">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="G1113" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41095,19 +41192,19 @@
         <v>1113</v>
       </c>
       <c r="B1114" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="C1114" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="D1114">
         <v>2024</v>
       </c>
       <c r="E1114" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="F1114" t="s">
-        <v>4080</v>
+        <v>4079</v>
       </c>
       <c r="G1114" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41120,19 +41217,19 @@
         <v>1114</v>
       </c>
       <c r="B1115" t="s">
+        <v>4068</v>
+      </c>
+      <c r="C1115" t="s">
         <v>4069</v>
-      </c>
-      <c r="C1115" t="s">
-        <v>4070</v>
       </c>
       <c r="D1115">
         <v>1979</v>
       </c>
       <c r="E1115" t="s">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="F1115" t="s">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="G1115" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41145,7 +41242,7 @@
         <v>1115</v>
       </c>
       <c r="B1116" t="s">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="C1116" t="s">
         <v>746</v>
@@ -41154,10 +41251,10 @@
         <v>1964</v>
       </c>
       <c r="E1116" t="s">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="F1116" t="s">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="G1116" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41170,19 +41267,19 @@
         <v>1116</v>
       </c>
       <c r="B1117" t="s">
+        <v>4074</v>
+      </c>
+      <c r="C1117" t="s">
         <v>4075</v>
-      </c>
-      <c r="C1117" t="s">
-        <v>4076</v>
       </c>
       <c r="D1117">
         <v>1993</v>
       </c>
       <c r="E1117" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="F1117" t="s">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="G1117" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41195,19 +41292,19 @@
         <v>1117</v>
       </c>
       <c r="B1118" t="s">
+        <v>4076</v>
+      </c>
+      <c r="C1118" t="s">
         <v>4077</v>
-      </c>
-      <c r="C1118" t="s">
-        <v>4078</v>
       </c>
       <c r="D1118">
         <v>1981</v>
       </c>
       <c r="E1118" t="s">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="F1118" t="s">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="G1118" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41220,7 +41317,7 @@
         <v>1118</v>
       </c>
       <c r="B1119" t="s">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="C1119" t="s">
         <v>127</v>
@@ -41229,10 +41326,10 @@
         <v>2024</v>
       </c>
       <c r="E1119" t="s">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="F1119" t="s">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="G1119" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41245,10 +41342,10 @@
         <v>1119</v>
       </c>
       <c r="B1120" t="s">
+        <v>4086</v>
+      </c>
+      <c r="C1120" t="s">
         <v>4087</v>
-      </c>
-      <c r="C1120" t="s">
-        <v>4088</v>
       </c>
       <c r="D1120">
         <v>2006</v>
@@ -41257,7 +41354,7 @@
         <v>151</v>
       </c>
       <c r="F1120" t="s">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="G1120" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41270,19 +41367,19 @@
         <v>1120</v>
       </c>
       <c r="B1121" t="s">
+        <v>4088</v>
+      </c>
+      <c r="C1121" t="s">
         <v>4089</v>
-      </c>
-      <c r="C1121" t="s">
-        <v>4090</v>
       </c>
       <c r="D1121">
         <v>1974</v>
       </c>
       <c r="E1121" t="s">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="F1121" t="s">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="G1121" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41295,19 +41392,19 @@
         <v>1121</v>
       </c>
       <c r="B1122" t="s">
+        <v>4091</v>
+      </c>
+      <c r="C1122" t="s">
         <v>4092</v>
-      </c>
-      <c r="C1122" t="s">
-        <v>4093</v>
       </c>
       <c r="D1122">
         <v>1974</v>
       </c>
       <c r="E1122" t="s">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="F1122" t="s">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="G1122" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41320,7 +41417,7 @@
         <v>1122</v>
       </c>
       <c r="B1123" t="s">
-        <v>4095</v>
+        <v>4094</v>
       </c>
       <c r="C1123" t="s">
         <v>2599</v>
@@ -41329,7 +41426,7 @@
         <v>2000</v>
       </c>
       <c r="E1123" t="s">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="F1123" t="s">
         <v>3925</v>
@@ -41345,7 +41442,7 @@
         <v>1123</v>
       </c>
       <c r="B1124" t="s">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="C1124" t="s">
         <v>2255</v>
@@ -41354,10 +41451,10 @@
         <v>1986</v>
       </c>
       <c r="E1124" t="s">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="F1124" t="s">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="G1124" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41370,19 +41467,19 @@
         <v>1124</v>
       </c>
       <c r="B1125" t="s">
+        <v>4098</v>
+      </c>
+      <c r="C1125" t="s">
         <v>4099</v>
-      </c>
-      <c r="C1125" t="s">
-        <v>4100</v>
       </c>
       <c r="D1125">
         <v>1952</v>
       </c>
       <c r="E1125" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="F1125" t="s">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="G1125" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41395,19 +41492,19 @@
         <v>1125</v>
       </c>
       <c r="B1126" t="s">
+        <v>4106</v>
+      </c>
+      <c r="C1126" t="s">
         <v>4107</v>
-      </c>
-      <c r="C1126" t="s">
-        <v>4108</v>
       </c>
       <c r="D1126">
         <v>1965</v>
       </c>
       <c r="E1126" t="s">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="F1126" t="s">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="G1126" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41420,19 +41517,19 @@
         <v>1126</v>
       </c>
       <c r="B1127" t="s">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="C1127" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="D1127">
         <v>1980</v>
       </c>
       <c r="E1127" t="s">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="F1127" t="s">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="G1127" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41445,10 +41542,10 @@
         <v>1127</v>
       </c>
       <c r="B1128" t="s">
+        <v>4111</v>
+      </c>
+      <c r="C1128" t="s">
         <v>4112</v>
-      </c>
-      <c r="C1128" t="s">
-        <v>4113</v>
       </c>
       <c r="D1128">
         <v>2006</v>
@@ -41457,7 +41554,7 @@
         <v>171</v>
       </c>
       <c r="F1128" t="s">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="G1128" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41470,19 +41567,19 @@
         <v>1128</v>
       </c>
       <c r="B1129" t="s">
+        <v>4113</v>
+      </c>
+      <c r="C1129" t="s">
         <v>4114</v>
-      </c>
-      <c r="C1129" t="s">
-        <v>4115</v>
       </c>
       <c r="D1129">
         <v>1993</v>
       </c>
       <c r="E1129" t="s">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="F1129" t="s">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="G1129" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41495,19 +41592,19 @@
         <v>1129</v>
       </c>
       <c r="B1130" t="s">
+        <v>4116</v>
+      </c>
+      <c r="C1130" t="s">
         <v>4117</v>
-      </c>
-      <c r="C1130" t="s">
-        <v>4118</v>
       </c>
       <c r="D1130">
         <v>1952</v>
       </c>
       <c r="E1130" t="s">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="F1130" t="s">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="G1130" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41520,19 +41617,19 @@
         <v>1130</v>
       </c>
       <c r="B1131" t="s">
+        <v>4119</v>
+      </c>
+      <c r="C1131" t="s">
         <v>4120</v>
-      </c>
-      <c r="C1131" t="s">
-        <v>4121</v>
       </c>
       <c r="D1131">
         <v>1997</v>
       </c>
       <c r="E1131" t="s">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="F1131" t="s">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="G1131" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41545,16 +41642,16 @@
         <v>1131</v>
       </c>
       <c r="B1132" t="s">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="D1132">
         <v>1992</v>
       </c>
       <c r="E1132" t="s">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="F1132" t="s">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="G1132" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41567,7 +41664,7 @@
         <v>1132</v>
       </c>
       <c r="B1133" t="s">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="C1133" t="s">
         <v>2072</v>
@@ -41579,7 +41676,7 @@
         <v>3818</v>
       </c>
       <c r="F1133" t="s">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="G1133" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41592,19 +41689,19 @@
         <v>1133</v>
       </c>
       <c r="B1134" t="s">
+        <v>4132</v>
+      </c>
+      <c r="C1134" t="s">
         <v>4133</v>
-      </c>
-      <c r="C1134" t="s">
-        <v>4134</v>
       </c>
       <c r="D1134">
         <v>1988</v>
       </c>
       <c r="E1134" t="s">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="F1134" t="s">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="G1134" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41617,19 +41714,19 @@
         <v>1134</v>
       </c>
       <c r="B1135" t="s">
+        <v>4135</v>
+      </c>
+      <c r="C1135" t="s">
         <v>4136</v>
-      </c>
-      <c r="C1135" t="s">
-        <v>4137</v>
       </c>
       <c r="D1135">
         <v>1993</v>
       </c>
       <c r="E1135" t="s">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="F1135" t="s">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="G1135" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41642,19 +41739,19 @@
         <v>1135</v>
       </c>
       <c r="B1136" t="s">
+        <v>4138</v>
+      </c>
+      <c r="C1136" t="s">
         <v>4139</v>
-      </c>
-      <c r="C1136" t="s">
-        <v>4140</v>
       </c>
       <c r="D1136">
         <v>1981</v>
       </c>
       <c r="E1136" t="s">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="F1136" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="G1136" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41667,16 +41764,16 @@
         <v>1136</v>
       </c>
       <c r="B1137" t="s">
+        <v>4141</v>
+      </c>
+      <c r="C1137" t="s">
         <v>4142</v>
-      </c>
-      <c r="C1137" t="s">
-        <v>4143</v>
       </c>
       <c r="D1137">
         <v>1976</v>
       </c>
       <c r="E1137" t="s">
-        <v>4144</v>
+        <v>4143</v>
       </c>
       <c r="F1137" t="s">
         <v>3898</v>
@@ -41692,7 +41789,7 @@
         <v>1137</v>
       </c>
       <c r="B1138" t="s">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="C1138" t="s">
         <v>2599</v>
@@ -41701,7 +41798,7 @@
         <v>2000</v>
       </c>
       <c r="E1138" t="s">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="F1138" t="s">
         <v>3925</v>
@@ -41717,7 +41814,7 @@
         <v>1138</v>
       </c>
       <c r="B1139" t="s">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="D1139">
         <v>2023</v>
@@ -41726,7 +41823,7 @@
         <v>3700</v>
       </c>
       <c r="F1139" t="s">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="G1139" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41739,7 +41836,7 @@
         <v>1139</v>
       </c>
       <c r="B1140" t="s">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="C1140" t="s">
         <v>614</v>
@@ -41751,7 +41848,7 @@
         <v>3700</v>
       </c>
       <c r="F1140" t="s">
-        <v>4165</v>
+        <v>4164</v>
       </c>
       <c r="G1140" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41764,19 +41861,19 @@
         <v>1140</v>
       </c>
       <c r="B1141" t="s">
+        <v>4153</v>
+      </c>
+      <c r="C1141" t="s">
         <v>4154</v>
-      </c>
-      <c r="C1141" t="s">
-        <v>4155</v>
       </c>
       <c r="D1141">
         <v>1998</v>
       </c>
       <c r="E1141" t="s">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="F1141" t="s">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="G1141" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41789,19 +41886,19 @@
         <v>1141</v>
       </c>
       <c r="B1142" t="s">
+        <v>4156</v>
+      </c>
+      <c r="C1142" t="s">
         <v>4157</v>
-      </c>
-      <c r="C1142" t="s">
-        <v>4158</v>
       </c>
       <c r="D1142">
         <v>2000</v>
       </c>
       <c r="E1142" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="F1142" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="G1142" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41814,19 +41911,19 @@
         <v>1142</v>
       </c>
       <c r="B1143" t="s">
+        <v>4159</v>
+      </c>
+      <c r="C1143" t="s">
         <v>4160</v>
-      </c>
-      <c r="C1143" t="s">
-        <v>4161</v>
       </c>
       <c r="D1143">
         <v>2011</v>
       </c>
       <c r="E1143" t="s">
-        <v>4162</v>
+        <v>4161</v>
       </c>
       <c r="F1143" t="s">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="G1143" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41839,16 +41936,16 @@
         <v>1143</v>
       </c>
       <c r="B1144" t="s">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="D1144">
         <v>1982</v>
       </c>
       <c r="E1144" t="s">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="F1144" t="s">
-        <v>4169</v>
+        <v>4168</v>
       </c>
       <c r="G1144" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41861,16 +41958,16 @@
         <v>1144</v>
       </c>
       <c r="B1145" t="s">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="D1145">
         <v>1997</v>
       </c>
       <c r="E1145" t="s">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="F1145" t="s">
-        <v>4182</v>
+        <v>4181</v>
       </c>
       <c r="G1145" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41883,7 +41980,7 @@
         <v>1145</v>
       </c>
       <c r="B1146" t="s">
-        <v>4172</v>
+        <v>4171</v>
       </c>
       <c r="C1146" t="s">
         <v>449</v>
@@ -41895,7 +41992,7 @@
         <v>3242</v>
       </c>
       <c r="F1146" t="s">
-        <v>4183</v>
+        <v>4182</v>
       </c>
       <c r="G1146" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41908,19 +42005,19 @@
         <v>1146</v>
       </c>
       <c r="B1147" t="s">
+        <v>4172</v>
+      </c>
+      <c r="C1147" t="s">
         <v>4173</v>
-      </c>
-      <c r="C1147" t="s">
-        <v>4174</v>
       </c>
       <c r="D1147">
         <v>2016</v>
       </c>
       <c r="E1147" t="s">
-        <v>4175</v>
+        <v>4174</v>
       </c>
       <c r="F1147" t="s">
-        <v>4184</v>
+        <v>4183</v>
       </c>
       <c r="G1147" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41933,19 +42030,19 @@
         <v>1147</v>
       </c>
       <c r="B1148" t="s">
+        <v>4175</v>
+      </c>
+      <c r="C1148" t="s">
         <v>4176</v>
-      </c>
-      <c r="C1148" t="s">
-        <v>4177</v>
       </c>
       <c r="D1148">
         <v>2000</v>
       </c>
       <c r="E1148" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
       <c r="F1148" t="s">
-        <v>4185</v>
+        <v>4184</v>
       </c>
       <c r="G1148" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41958,19 +42055,19 @@
         <v>1148</v>
       </c>
       <c r="B1149" t="s">
+        <v>4178</v>
+      </c>
+      <c r="C1149" t="s">
         <v>4179</v>
-      </c>
-      <c r="C1149" t="s">
-        <v>4180</v>
       </c>
       <c r="D1149">
         <v>2000</v>
       </c>
       <c r="E1149" t="s">
-        <v>4181</v>
+        <v>4180</v>
       </c>
       <c r="F1149" t="s">
-        <v>4186</v>
+        <v>4185</v>
       </c>
       <c r="G1149" s="3" t="str">
         <f t="shared" si="34"/>
@@ -41983,19 +42080,19 @@
         <v>1149</v>
       </c>
       <c r="B1150" t="s">
+        <v>4186</v>
+      </c>
+      <c r="C1150" t="s">
         <v>4187</v>
-      </c>
-      <c r="C1150" t="s">
-        <v>4188</v>
       </c>
       <c r="D1150">
         <v>1989</v>
       </c>
       <c r="E1150" t="s">
-        <v>4192</v>
+        <v>4191</v>
       </c>
       <c r="F1150" t="s">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="G1150" s="3" t="str">
         <f t="shared" si="34"/>
@@ -42008,19 +42105,19 @@
         <v>1150</v>
       </c>
       <c r="B1151" t="s">
+        <v>4188</v>
+      </c>
+      <c r="C1151" t="s">
         <v>4189</v>
-      </c>
-      <c r="C1151" t="s">
-        <v>4190</v>
       </c>
       <c r="D1151">
         <v>1982</v>
       </c>
       <c r="E1151" t="s">
-        <v>4191</v>
+        <v>4190</v>
       </c>
       <c r="F1151" t="s">
-        <v>4205</v>
+        <v>4204</v>
       </c>
       <c r="G1151" s="3" t="str">
         <f t="shared" si="34"/>
@@ -42033,7 +42130,7 @@
         <v>1151</v>
       </c>
       <c r="B1152" t="s">
-        <v>4193</v>
+        <v>4192</v>
       </c>
       <c r="C1152" t="s">
         <v>3237</v>
@@ -42042,10 +42139,10 @@
         <v>1974</v>
       </c>
       <c r="E1152" t="s">
-        <v>4194</v>
+        <v>4193</v>
       </c>
       <c r="F1152" t="s">
-        <v>4206</v>
+        <v>4205</v>
       </c>
       <c r="G1152" s="3" t="str">
         <f t="shared" si="34"/>
@@ -42058,7 +42155,7 @@
         <v>1152</v>
       </c>
       <c r="B1153" t="s">
-        <v>4196</v>
+        <v>4195</v>
       </c>
       <c r="C1153" t="s">
         <v>614</v>
@@ -42067,10 +42164,10 @@
         <v>2004</v>
       </c>
       <c r="E1153" t="s">
-        <v>4195</v>
+        <v>4194</v>
       </c>
       <c r="F1153" t="s">
-        <v>4207</v>
+        <v>4206</v>
       </c>
       <c r="G1153" s="3" t="str">
         <f t="shared" si="34"/>
@@ -42083,7 +42180,7 @@
         <v>1153</v>
       </c>
       <c r="B1154" t="s">
-        <v>4197</v>
+        <v>4196</v>
       </c>
       <c r="C1154" t="s">
         <v>1935</v>
@@ -42092,10 +42189,10 @@
         <v>2001</v>
       </c>
       <c r="E1154" t="s">
-        <v>4198</v>
+        <v>4197</v>
       </c>
       <c r="F1154" t="s">
-        <v>4208</v>
+        <v>4207</v>
       </c>
       <c r="G1154" s="3" t="str">
         <f t="shared" si="34"/>
@@ -42108,7 +42205,7 @@
         <v>1154</v>
       </c>
       <c r="B1155" t="s">
-        <v>4199</v>
+        <v>4198</v>
       </c>
       <c r="C1155" t="s">
         <v>2244</v>
@@ -42117,13 +42214,13 @@
         <v>1983</v>
       </c>
       <c r="E1155" t="s">
-        <v>4200</v>
+        <v>4199</v>
       </c>
       <c r="F1155" t="s">
-        <v>4209</v>
+        <v>4208</v>
       </c>
       <c r="G1155" s="3" t="str">
-        <f t="shared" ref="G1155:G1163" si="36">HYPERLINK(F1155)</f>
+        <f t="shared" ref="G1155:G1170" si="36">HYPERLINK(F1155)</f>
         <v>https://mariantoc.github.io/Notas-Geologicas-2025/structural.html#SchubertC1983</v>
       </c>
     </row>
@@ -42133,19 +42230,19 @@
         <v>1155</v>
       </c>
       <c r="B1156" t="s">
+        <v>4200</v>
+      </c>
+      <c r="C1156" t="s">
         <v>4201</v>
-      </c>
-      <c r="C1156" t="s">
-        <v>4202</v>
       </c>
       <c r="D1156">
         <v>2002</v>
       </c>
       <c r="E1156" t="s">
-        <v>4203</v>
+        <v>4202</v>
       </c>
       <c r="F1156" t="s">
-        <v>4210</v>
+        <v>4209</v>
       </c>
       <c r="G1156" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42158,19 +42255,19 @@
         <v>1156</v>
       </c>
       <c r="B1157" t="s">
+        <v>4210</v>
+      </c>
+      <c r="C1157" t="s">
         <v>4211</v>
-      </c>
-      <c r="C1157" t="s">
-        <v>4212</v>
       </c>
       <c r="D1157">
         <v>2001</v>
       </c>
       <c r="E1157" t="s">
-        <v>4213</v>
-      </c>
-      <c r="F1157" s="5" t="s">
-        <v>4228</v>
+        <v>4212</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>4227</v>
       </c>
       <c r="G1157" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42179,23 +42276,23 @@
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1158">
-        <f t="shared" ref="A1158:A1163" si="37">A1157+1</f>
+        <f t="shared" ref="A1158:A1170" si="37">A1157+1</f>
         <v>1157</v>
       </c>
       <c r="B1158" t="s">
+        <v>4213</v>
+      </c>
+      <c r="C1158" t="s">
         <v>4214</v>
-      </c>
-      <c r="C1158" t="s">
-        <v>4215</v>
       </c>
       <c r="D1158">
         <v>1994</v>
       </c>
       <c r="E1158" t="s">
-        <v>4216</v>
-      </c>
-      <c r="F1158" s="5" t="s">
-        <v>4229</v>
+        <v>4215</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>4228</v>
       </c>
       <c r="G1158" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42208,19 +42305,19 @@
         <v>1158</v>
       </c>
       <c r="B1159" t="s">
-        <v>4217</v>
+        <v>4216</v>
       </c>
       <c r="C1159" t="s">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="D1159">
         <v>2002</v>
       </c>
       <c r="E1159" t="s">
-        <v>4218</v>
-      </c>
-      <c r="F1159" s="5" t="s">
-        <v>4230</v>
+        <v>4217</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>4229</v>
       </c>
       <c r="G1159" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42233,7 +42330,7 @@
         <v>1159</v>
       </c>
       <c r="B1160" t="s">
-        <v>4219</v>
+        <v>4218</v>
       </c>
       <c r="C1160" t="s">
         <v>22</v>
@@ -42242,10 +42339,10 @@
         <v>1989</v>
       </c>
       <c r="E1160" t="s">
-        <v>4220</v>
-      </c>
-      <c r="F1160" s="5" t="s">
-        <v>4231</v>
+        <v>4219</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>4230</v>
       </c>
       <c r="G1160" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42258,19 +42355,19 @@
         <v>1160</v>
       </c>
       <c r="B1161" t="s">
+        <v>4220</v>
+      </c>
+      <c r="C1161" t="s">
         <v>4221</v>
-      </c>
-      <c r="C1161" t="s">
-        <v>4222</v>
       </c>
       <c r="D1161">
         <v>2013</v>
       </c>
       <c r="E1161" t="s">
-        <v>4223</v>
-      </c>
-      <c r="F1161" s="5" t="s">
-        <v>4232</v>
+        <v>4222</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>4231</v>
       </c>
       <c r="G1161" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42283,19 +42380,19 @@
         <v>1161</v>
       </c>
       <c r="B1162" t="s">
+        <v>4223</v>
+      </c>
+      <c r="C1162" t="s">
         <v>4224</v>
-      </c>
-      <c r="C1162" t="s">
-        <v>4225</v>
       </c>
       <c r="D1162">
         <v>1997</v>
       </c>
       <c r="E1162" t="s">
-        <v>4226</v>
-      </c>
-      <c r="F1162" s="5" t="s">
-        <v>4233</v>
+        <v>4225</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>4232</v>
       </c>
       <c r="G1162" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42308,7 +42405,7 @@
         <v>1162</v>
       </c>
       <c r="B1163" t="s">
-        <v>4227</v>
+        <v>4226</v>
       </c>
       <c r="C1163" t="s">
         <v>2861</v>
@@ -42317,10 +42414,10 @@
         <v>1996</v>
       </c>
       <c r="E1163" t="s">
+        <v>4233</v>
+      </c>
+      <c r="F1163" t="s">
         <v>4234</v>
-      </c>
-      <c r="F1163" s="5" t="s">
-        <v>4235</v>
       </c>
       <c r="G1163" s="3" t="str">
         <f t="shared" si="36"/>
@@ -42328,29 +42425,193 @@
       </c>
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1164">
+        <f t="shared" si="37"/>
+        <v>1163</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>4235</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>4236</v>
+      </c>
+      <c r="D1164">
+        <v>2026</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>4237</v>
+      </c>
       <c r="F1164" s="3" t="s">
-        <v>3931</v>
+        <v>4254</v>
+      </c>
+      <c r="G1164" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#JuszcykKRzenik202S6</v>
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1165">
+        <f t="shared" si="37"/>
+        <v>1164</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>4238</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>4239</v>
+      </c>
+      <c r="D1165">
+        <v>1954</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>4240</v>
+      </c>
       <c r="F1165" s="3" t="s">
-        <v>3931</v>
+        <v>4255</v>
+      </c>
+      <c r="G1165" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/fields.html#SugarE1954</v>
       </c>
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1166">
+        <f t="shared" si="37"/>
+        <v>1165</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>4241</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>4242</v>
+      </c>
+      <c r="D1166">
+        <v>1972</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>4243</v>
+      </c>
       <c r="F1166" s="3" t="s">
-        <v>3931</v>
+        <v>4256</v>
+      </c>
+      <c r="G1166" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/minerals.html#ZosayaD1972</v>
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1167">
+        <f t="shared" si="37"/>
+        <v>1166</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>4244</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>4245</v>
+      </c>
+      <c r="D1167">
+        <v>1973</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>4246</v>
+      </c>
       <c r="F1167" s="3" t="s">
-        <v>3931</v>
+        <v>4257</v>
+      </c>
+      <c r="G1167" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#GameroG1973</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1168">
+        <f t="shared" si="37"/>
+        <v>1167</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>4247</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1168">
+        <v>2023</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>4248</v>
+      </c>
+      <c r="F1168" s="3" t="s">
+        <v>4258</v>
+      </c>
+      <c r="G1168" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/biography.html#RodriguezJA2023</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1169">
+        <f t="shared" si="37"/>
+        <v>1168</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>4249</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D1169">
+        <v>1971</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>4250</v>
+      </c>
+      <c r="F1169" s="3" t="s">
+        <v>4259</v>
+      </c>
+      <c r="G1169" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/stratigraphy.html#MacsotayO1971</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1170">
+        <f t="shared" si="37"/>
+        <v>1169</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>4251</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>4252</v>
+      </c>
+      <c r="D1170">
+        <v>1987</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>4253</v>
+      </c>
+      <c r="F1170" s="3" t="s">
+        <v>4260</v>
+      </c>
+      <c r="G1170" s="3" t="str">
+        <f t="shared" si="36"/>
+        <v>https://mariantoc.github.io/Notas-Geologicas-2025/ecology.html#JacomeJC1987</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1167" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F1167" r:id="rId1" location="GameroG1973" xr:uid="{82DE44F7-E6B9-4F8F-92E5-98EBC94F994B}"/>
+    <hyperlink ref="F1164" r:id="rId2" location="JuszcykKRzenik202S6" xr:uid="{E8518A5D-D9B7-42E8-924D-4FAA2422B4E2}"/>
+    <hyperlink ref="F1165" r:id="rId3" location="SugarE1954" xr:uid="{4A33A262-0F4B-4F1C-99A7-997489B86EEC}"/>
+    <hyperlink ref="F1166" r:id="rId4" location="ZosayaD1972" xr:uid="{D5CB4971-4F15-45D5-B0B5-AC1A0934CD44}"/>
+    <hyperlink ref="F1168" r:id="rId5" location="RodriguezJA2023" xr:uid="{7D48D9F9-C7D1-4766-8AFD-4083E7384F1E}"/>
+    <hyperlink ref="F1169" r:id="rId6" location="MacsotayO1971" xr:uid="{A60A1E08-4E9A-4466-AEE7-6972EEC961AC}"/>
+    <hyperlink ref="F1170" r:id="rId7" location="JacomeJC1987" xr:uid="{D208BBD9-7AB0-467B-98AB-8096B5FEE597}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>